--- a/SpaceDebris_site_1000/unknown_LARES_AHSS_attached_to_Vega_AVUM_stage.xlsx
+++ b/SpaceDebris_site_1000/unknown_LARES_AHSS_attached_to_Vega_AVUM_stage.xlsx
@@ -452,7002 +452,7002 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131.44</v>
+        <v>0.31</v>
       </c>
       <c r="B2" t="n">
-        <v>23479</v>
+        <v>37534</v>
       </c>
       <c r="C2" t="n">
-        <v>134.72</v>
+        <v>6.69</v>
       </c>
       <c r="D2" t="n">
-        <v>18230</v>
+        <v>10921</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>139.52</v>
+        <v>0.38</v>
       </c>
       <c r="B3" t="n">
-        <v>23044</v>
+        <v>37691</v>
       </c>
       <c r="C3" t="n">
-        <v>143.88</v>
+        <v>2.43</v>
       </c>
       <c r="D3" t="n">
-        <v>24125</v>
+        <v>24613</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>140.83</v>
+        <v>0.72</v>
       </c>
       <c r="B4" t="n">
-        <v>23796</v>
+        <v>36579</v>
       </c>
       <c r="C4" t="n">
-        <v>144.45</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>24219</v>
+        <v>14144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3.51</v>
+        <v>1.09</v>
       </c>
       <c r="B5" t="n">
-        <v>24434</v>
+        <v>38960</v>
       </c>
       <c r="C5" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10732</v>
+        <v>20726</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99.2</v>
+        <v>1.4</v>
       </c>
       <c r="B6" t="n">
-        <v>43482</v>
+        <v>37199</v>
       </c>
       <c r="C6" t="n">
-        <v>100.73</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>22276</v>
+        <v>21980</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117.74</v>
+        <v>1.46</v>
       </c>
       <c r="B7" t="n">
-        <v>20428</v>
+        <v>37556</v>
       </c>
       <c r="C7" t="n">
-        <v>114.95</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>22660</v>
+        <v>27724</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>92.25</v>
+        <v>2.01</v>
       </c>
       <c r="B8" t="n">
-        <v>26457</v>
+        <v>37559</v>
       </c>
       <c r="C8" t="n">
-        <v>91.73</v>
+        <v>4.31</v>
       </c>
       <c r="D8" t="n">
-        <v>12516</v>
+        <v>26075</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106.72</v>
+        <v>2.05</v>
       </c>
       <c r="B9" t="n">
-        <v>43114</v>
+        <v>37623</v>
       </c>
       <c r="C9" t="n">
-        <v>108.31</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>28751</v>
+        <v>19596</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>90.81999999999999</v>
+        <v>2.07</v>
       </c>
       <c r="B10" t="n">
-        <v>25287</v>
+        <v>36315</v>
       </c>
       <c r="C10" t="n">
-        <v>88.41</v>
+        <v>1.01</v>
       </c>
       <c r="D10" t="n">
-        <v>10125</v>
+        <v>17259</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95.13</v>
+        <v>2.94</v>
       </c>
       <c r="B11" t="n">
-        <v>33942</v>
+        <v>35925</v>
       </c>
       <c r="C11" t="n">
-        <v>96.7</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>14986</v>
+        <v>29779</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105.2</v>
+        <v>4</v>
       </c>
       <c r="B12" t="n">
-        <v>44897</v>
+        <v>34982</v>
       </c>
       <c r="C12" t="n">
-        <v>109.59</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>28850</v>
+        <v>15485</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102.47</v>
+        <v>4.46</v>
       </c>
       <c r="B13" t="n">
-        <v>48368</v>
+        <v>36013</v>
       </c>
       <c r="C13" t="n">
-        <v>105.16</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>15231</v>
+        <v>13234</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111.44</v>
+        <v>5.03</v>
       </c>
       <c r="B14" t="n">
-        <v>28271</v>
+        <v>34879</v>
       </c>
       <c r="C14" t="n">
-        <v>110.77</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>12865</v>
+        <v>16202</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110</v>
+        <v>5.07</v>
       </c>
       <c r="B15" t="n">
-        <v>30950</v>
+        <v>34448</v>
       </c>
       <c r="C15" t="n">
-        <v>108.17</v>
+        <v>9.98</v>
       </c>
       <c r="D15" t="n">
-        <v>20940</v>
+        <v>20791</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97.03</v>
+        <v>5.24</v>
       </c>
       <c r="B16" t="n">
-        <v>38520</v>
+        <v>36160</v>
       </c>
       <c r="C16" t="n">
-        <v>93.83</v>
+        <v>1.78</v>
       </c>
       <c r="D16" t="n">
-        <v>23905</v>
+        <v>15802</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>77.59999999999999</v>
+        <v>5.87</v>
       </c>
       <c r="B17" t="n">
-        <v>24039</v>
+        <v>33125</v>
       </c>
       <c r="C17" t="n">
-        <v>76.75</v>
+        <v>7.62</v>
       </c>
       <c r="D17" t="n">
-        <v>26145</v>
+        <v>27771</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109.61</v>
+        <v>5.9</v>
       </c>
       <c r="B18" t="n">
-        <v>35271</v>
+        <v>34119</v>
       </c>
       <c r="C18" t="n">
-        <v>113.26</v>
+        <v>8.67</v>
       </c>
       <c r="D18" t="n">
-        <v>26016</v>
+        <v>24380</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>92.61</v>
+        <v>5.96</v>
       </c>
       <c r="B19" t="n">
-        <v>29702</v>
+        <v>33788</v>
       </c>
       <c r="C19" t="n">
-        <v>95.87</v>
+        <v>11.27</v>
       </c>
       <c r="D19" t="n">
-        <v>16043</v>
+        <v>22383</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>101.2</v>
+        <v>6.14</v>
       </c>
       <c r="B20" t="n">
-        <v>43176</v>
+        <v>34021</v>
       </c>
       <c r="C20" t="n">
-        <v>97.95</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>14940</v>
+        <v>17268</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95.75</v>
+        <v>7.49</v>
       </c>
       <c r="B21" t="n">
-        <v>35798</v>
+        <v>34514</v>
       </c>
       <c r="C21" t="n">
-        <v>98.56999999999999</v>
+        <v>3.21</v>
       </c>
       <c r="D21" t="n">
-        <v>25512</v>
+        <v>21303</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>99.59999999999999</v>
+        <v>7.51</v>
       </c>
       <c r="B22" t="n">
-        <v>43026</v>
+        <v>33381</v>
       </c>
       <c r="C22" t="n">
-        <v>98.14</v>
+        <v>7.28</v>
       </c>
       <c r="D22" t="n">
-        <v>13391</v>
+        <v>24111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>100.11</v>
+        <v>7.77</v>
       </c>
       <c r="B23" t="n">
-        <v>44841</v>
+        <v>33501</v>
       </c>
       <c r="C23" t="n">
-        <v>103.69</v>
+        <v>0.37</v>
       </c>
       <c r="D23" t="n">
-        <v>23101</v>
+        <v>22322</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>98.38</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="B24" t="n">
-        <v>41427</v>
+        <v>32798</v>
       </c>
       <c r="C24" t="n">
-        <v>96.38</v>
+        <v>15.16</v>
       </c>
       <c r="D24" t="n">
-        <v>18196</v>
+        <v>21881</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110.04</v>
+        <v>8.19</v>
       </c>
       <c r="B25" t="n">
-        <v>33733</v>
+        <v>33778</v>
       </c>
       <c r="C25" t="n">
-        <v>107.33</v>
+        <v>9.48</v>
       </c>
       <c r="D25" t="n">
-        <v>17788</v>
+        <v>17005</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104.63</v>
+        <v>8.26</v>
       </c>
       <c r="B26" t="n">
-        <v>47870</v>
+        <v>31814</v>
       </c>
       <c r="C26" t="n">
-        <v>103.73</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>25110</v>
+        <v>24683</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>92.59999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="B27" t="n">
-        <v>24860</v>
+        <v>32714</v>
       </c>
       <c r="C27" t="n">
-        <v>91.81999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>26701</v>
+        <v>20925</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111.15</v>
+        <v>9.75</v>
       </c>
       <c r="B28" t="n">
-        <v>27865</v>
+        <v>33524</v>
       </c>
       <c r="C28" t="n">
-        <v>109.07</v>
+        <v>14.43</v>
       </c>
       <c r="D28" t="n">
-        <v>28091</v>
+        <v>23478</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96.68000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="B29" t="n">
-        <v>39988</v>
+        <v>29606</v>
       </c>
       <c r="C29" t="n">
-        <v>100.33</v>
+        <v>7.56</v>
       </c>
       <c r="D29" t="n">
-        <v>13863</v>
+        <v>23128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>92.59</v>
+        <v>10.42</v>
       </c>
       <c r="B30" t="n">
-        <v>28150</v>
+        <v>31992</v>
       </c>
       <c r="C30" t="n">
-        <v>90.77</v>
+        <v>10.1</v>
       </c>
       <c r="D30" t="n">
-        <v>20599</v>
+        <v>21651</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111.88</v>
+        <v>10.81</v>
       </c>
       <c r="B31" t="n">
-        <v>29983</v>
+        <v>30107</v>
       </c>
       <c r="C31" t="n">
-        <v>113.86</v>
+        <v>8.4</v>
       </c>
       <c r="D31" t="n">
-        <v>22737</v>
+        <v>19707</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>107.68</v>
+        <v>11.08</v>
       </c>
       <c r="B32" t="n">
-        <v>41897</v>
+        <v>28955</v>
       </c>
       <c r="C32" t="n">
-        <v>108.24</v>
+        <v>4.03</v>
       </c>
       <c r="D32" t="n">
-        <v>19914</v>
+        <v>12491</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110.08</v>
+        <v>11.27</v>
       </c>
       <c r="B33" t="n">
-        <v>32893</v>
+        <v>29916</v>
       </c>
       <c r="C33" t="n">
-        <v>113.29</v>
+        <v>18.46</v>
       </c>
       <c r="D33" t="n">
-        <v>10868</v>
+        <v>14317</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96.41</v>
+        <v>11.73</v>
       </c>
       <c r="B34" t="n">
-        <v>36316</v>
+        <v>29816</v>
       </c>
       <c r="C34" t="n">
-        <v>98.06999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="D34" t="n">
-        <v>15983</v>
+        <v>26280</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96.63</v>
+        <v>11.8</v>
       </c>
       <c r="B35" t="n">
-        <v>38001</v>
+        <v>27854</v>
       </c>
       <c r="C35" t="n">
-        <v>100.02</v>
+        <v>7.79</v>
       </c>
       <c r="D35" t="n">
-        <v>24885</v>
+        <v>24099</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>138.3</v>
+        <v>12.2</v>
       </c>
       <c r="B36" t="n">
-        <v>23545</v>
+        <v>30089</v>
       </c>
       <c r="C36" t="n">
-        <v>143.21</v>
+        <v>6.01</v>
       </c>
       <c r="D36" t="n">
-        <v>12060</v>
+        <v>25406</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111.9</v>
+        <v>12.6</v>
       </c>
       <c r="B37" t="n">
-        <v>29752</v>
+        <v>25424</v>
       </c>
       <c r="C37" t="n">
-        <v>115.49</v>
+        <v>7.69</v>
       </c>
       <c r="D37" t="n">
-        <v>13912</v>
+        <v>25544</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>94.73</v>
+        <v>13</v>
       </c>
       <c r="B38" t="n">
-        <v>33636</v>
+        <v>25742</v>
       </c>
       <c r="C38" t="n">
-        <v>96.73999999999999</v>
+        <v>2.95</v>
       </c>
       <c r="D38" t="n">
-        <v>24382</v>
+        <v>22569</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113.26</v>
+        <v>13</v>
       </c>
       <c r="B39" t="n">
-        <v>24229</v>
+        <v>28651</v>
       </c>
       <c r="C39" t="n">
-        <v>112.66</v>
+        <v>18.74</v>
       </c>
       <c r="D39" t="n">
-        <v>25549</v>
+        <v>16134</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112.51</v>
+        <v>13.53</v>
       </c>
       <c r="B40" t="n">
-        <v>27459</v>
+        <v>26580</v>
       </c>
       <c r="C40" t="n">
-        <v>113</v>
+        <v>21.74</v>
       </c>
       <c r="D40" t="n">
-        <v>12880</v>
+        <v>14985</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>108.36</v>
+        <v>14.33</v>
       </c>
       <c r="B41" t="n">
-        <v>41011</v>
+        <v>27887</v>
       </c>
       <c r="C41" t="n">
-        <v>109.47</v>
+        <v>23.87</v>
       </c>
       <c r="D41" t="n">
-        <v>26187</v>
+        <v>12866</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>114.78</v>
+        <v>14.42</v>
       </c>
       <c r="B42" t="n">
-        <v>25931</v>
+        <v>27622</v>
       </c>
       <c r="C42" t="n">
-        <v>111.68</v>
+        <v>23.64</v>
       </c>
       <c r="D42" t="n">
-        <v>20469</v>
+        <v>29158</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115.19</v>
+        <v>14.53</v>
       </c>
       <c r="B43" t="n">
-        <v>23857</v>
+        <v>28782</v>
       </c>
       <c r="C43" t="n">
-        <v>115.85</v>
+        <v>14.69</v>
       </c>
       <c r="D43" t="n">
-        <v>10374</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>102.86</v>
+        <v>14.72</v>
       </c>
       <c r="B44" t="n">
-        <v>47385</v>
+        <v>26436</v>
       </c>
       <c r="C44" t="n">
-        <v>100.14</v>
+        <v>17.62</v>
       </c>
       <c r="D44" t="n">
-        <v>28987</v>
+        <v>10955</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>91.53</v>
+        <v>15.09</v>
       </c>
       <c r="B45" t="n">
-        <v>24699</v>
+        <v>27908</v>
       </c>
       <c r="C45" t="n">
-        <v>88.69</v>
+        <v>18.45</v>
       </c>
       <c r="D45" t="n">
-        <v>19078</v>
+        <v>11880</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>95</v>
+        <v>15.23</v>
       </c>
       <c r="B46" t="n">
-        <v>37098</v>
+        <v>25839</v>
       </c>
       <c r="C46" t="n">
-        <v>95.52</v>
+        <v>4.8</v>
       </c>
       <c r="D46" t="n">
-        <v>10975</v>
+        <v>28904</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>94.20999999999999</v>
+        <v>15.57</v>
       </c>
       <c r="B47" t="n">
-        <v>32611</v>
+        <v>25866</v>
       </c>
       <c r="C47" t="n">
-        <v>94.64</v>
+        <v>22.32</v>
       </c>
       <c r="D47" t="n">
-        <v>26689</v>
+        <v>16367</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>102.45</v>
+        <v>16.1</v>
       </c>
       <c r="B48" t="n">
-        <v>45647</v>
+        <v>27499</v>
       </c>
       <c r="C48" t="n">
-        <v>100.13</v>
+        <v>24.56</v>
       </c>
       <c r="D48" t="n">
-        <v>19487</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>110.88</v>
+        <v>16.26</v>
       </c>
       <c r="B49" t="n">
-        <v>31904</v>
+        <v>29632</v>
       </c>
       <c r="C49" t="n">
-        <v>114.51</v>
+        <v>17.96</v>
       </c>
       <c r="D49" t="n">
-        <v>14827</v>
+        <v>14944</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>106.3</v>
+        <v>16.47</v>
       </c>
       <c r="B50" t="n">
-        <v>43226</v>
+        <v>24893</v>
       </c>
       <c r="C50" t="n">
-        <v>107.28</v>
+        <v>13.8</v>
       </c>
       <c r="D50" t="n">
-        <v>17236</v>
+        <v>11944</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>26.23</v>
+        <v>16.49</v>
       </c>
       <c r="B51" t="n">
-        <v>24108</v>
+        <v>26517</v>
       </c>
       <c r="C51" t="n">
-        <v>25.61</v>
+        <v>14.89</v>
       </c>
       <c r="D51" t="n">
-        <v>17533</v>
+        <v>13693</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>114.8</v>
+        <v>16.75</v>
       </c>
       <c r="B52" t="n">
-        <v>22252</v>
+        <v>26060</v>
       </c>
       <c r="C52" t="n">
-        <v>115.26</v>
+        <v>13.82</v>
       </c>
       <c r="D52" t="n">
-        <v>22386</v>
+        <v>22705</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>110.56</v>
+        <v>16.9</v>
       </c>
       <c r="B53" t="n">
-        <v>31895</v>
+        <v>26166</v>
       </c>
       <c r="C53" t="n">
-        <v>114.36</v>
+        <v>15.23</v>
       </c>
       <c r="D53" t="n">
-        <v>24975</v>
+        <v>16948</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>108.36</v>
+        <v>16.93</v>
       </c>
       <c r="B54" t="n">
-        <v>35749</v>
+        <v>24739</v>
       </c>
       <c r="C54" t="n">
-        <v>107.49</v>
+        <v>15.81</v>
       </c>
       <c r="D54" t="n">
-        <v>28926</v>
+        <v>12125</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112.51</v>
+        <v>17.13</v>
       </c>
       <c r="B55" t="n">
-        <v>26476</v>
+        <v>23046</v>
       </c>
       <c r="C55" t="n">
-        <v>114.48</v>
+        <v>25.33</v>
       </c>
       <c r="D55" t="n">
-        <v>24746</v>
+        <v>29847</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>93.36</v>
+        <v>17.52</v>
       </c>
       <c r="B56" t="n">
-        <v>26582</v>
+        <v>26165</v>
       </c>
       <c r="C56" t="n">
-        <v>95.79000000000001</v>
+        <v>20.21</v>
       </c>
       <c r="D56" t="n">
-        <v>22937</v>
+        <v>18155</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>111.8</v>
+        <v>17.63</v>
       </c>
       <c r="B57" t="n">
-        <v>27071</v>
+        <v>24934</v>
       </c>
       <c r="C57" t="n">
-        <v>112.01</v>
+        <v>16.42</v>
       </c>
       <c r="D57" t="n">
-        <v>12949</v>
+        <v>11111</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>105.16</v>
+        <v>18.04</v>
       </c>
       <c r="B58" t="n">
-        <v>45980</v>
+        <v>24766</v>
       </c>
       <c r="C58" t="n">
-        <v>101.44</v>
+        <v>14.53</v>
       </c>
       <c r="D58" t="n">
-        <v>17121</v>
+        <v>23342</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>90.15000000000001</v>
+        <v>18.57</v>
       </c>
       <c r="B59" t="n">
-        <v>22438</v>
+        <v>24230</v>
       </c>
       <c r="C59" t="n">
-        <v>91.39</v>
+        <v>18.65</v>
       </c>
       <c r="D59" t="n">
-        <v>11474</v>
+        <v>25047</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>105.55</v>
+        <v>20.2</v>
       </c>
       <c r="B60" t="n">
-        <v>43934</v>
+        <v>23548</v>
       </c>
       <c r="C60" t="n">
-        <v>102.6</v>
+        <v>15.2</v>
       </c>
       <c r="D60" t="n">
-        <v>22943</v>
+        <v>11123</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>94.40000000000001</v>
+        <v>20.21</v>
       </c>
       <c r="B61" t="n">
-        <v>31560</v>
+        <v>23131</v>
       </c>
       <c r="C61" t="n">
-        <v>94.08</v>
+        <v>23.09</v>
       </c>
       <c r="D61" t="n">
-        <v>21000</v>
+        <v>28662</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113.25</v>
+        <v>20.34</v>
       </c>
       <c r="B62" t="n">
-        <v>23614</v>
+        <v>25057</v>
       </c>
       <c r="C62" t="n">
-        <v>110.6</v>
+        <v>27.63</v>
       </c>
       <c r="D62" t="n">
-        <v>28575</v>
+        <v>27244</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>104.34</v>
+        <v>20.47</v>
       </c>
       <c r="B63" t="n">
-        <v>43368</v>
+        <v>23996</v>
       </c>
       <c r="C63" t="n">
-        <v>105.34</v>
+        <v>20.83</v>
       </c>
       <c r="D63" t="n">
-        <v>11896</v>
+        <v>24219</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>92.39</v>
+        <v>21.31</v>
       </c>
       <c r="B64" t="n">
-        <v>27599</v>
+        <v>24769</v>
       </c>
       <c r="C64" t="n">
-        <v>89.64</v>
+        <v>27.88</v>
       </c>
       <c r="D64" t="n">
-        <v>12791</v>
+        <v>11414</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>96.31</v>
+        <v>21.35</v>
       </c>
       <c r="B65" t="n">
-        <v>35231</v>
+        <v>21684</v>
       </c>
       <c r="C65" t="n">
-        <v>98.04000000000001</v>
+        <v>23.31</v>
       </c>
       <c r="D65" t="n">
-        <v>28752</v>
+        <v>17205</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>95</v>
+        <v>21.39</v>
       </c>
       <c r="B66" t="n">
-        <v>35531</v>
+        <v>21830</v>
       </c>
       <c r="C66" t="n">
-        <v>98.27</v>
+        <v>26.1</v>
       </c>
       <c r="D66" t="n">
-        <v>13312</v>
+        <v>10931</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>166.11</v>
+        <v>21.99</v>
       </c>
       <c r="B67" t="n">
-        <v>22951</v>
+        <v>23132</v>
       </c>
       <c r="C67" t="n">
-        <v>161.92</v>
+        <v>13.76</v>
       </c>
       <c r="D67" t="n">
-        <v>19204</v>
+        <v>19891</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>104.68</v>
+        <v>22.3</v>
       </c>
       <c r="B68" t="n">
-        <v>46391</v>
+        <v>24250</v>
       </c>
       <c r="C68" t="n">
-        <v>105.54</v>
+        <v>19.87</v>
       </c>
       <c r="D68" t="n">
-        <v>21266</v>
+        <v>14340</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>94.5</v>
+        <v>23.36</v>
       </c>
       <c r="B69" t="n">
-        <v>33908</v>
+        <v>22222</v>
       </c>
       <c r="C69" t="n">
-        <v>89.97</v>
+        <v>26.31</v>
       </c>
       <c r="D69" t="n">
-        <v>11920</v>
+        <v>10132</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>97.58</v>
+        <v>23.42</v>
       </c>
       <c r="B70" t="n">
-        <v>42294</v>
+        <v>21375</v>
       </c>
       <c r="C70" t="n">
-        <v>95.44</v>
+        <v>24.21</v>
       </c>
       <c r="D70" t="n">
-        <v>29365</v>
+        <v>25980</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>90.48999999999999</v>
+        <v>24.68</v>
       </c>
       <c r="B71" t="n">
-        <v>24668</v>
+        <v>22089</v>
       </c>
       <c r="C71" t="n">
-        <v>88.62</v>
+        <v>23.04</v>
       </c>
       <c r="D71" t="n">
-        <v>25456</v>
+        <v>12578</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>110.13</v>
+        <v>25.52</v>
       </c>
       <c r="B72" t="n">
-        <v>34774</v>
+        <v>23084</v>
       </c>
       <c r="C72" t="n">
-        <v>112.6</v>
+        <v>26.21</v>
       </c>
       <c r="D72" t="n">
-        <v>19387</v>
+        <v>26789</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113.03</v>
+        <v>25.71</v>
       </c>
       <c r="B73" t="n">
-        <v>23971</v>
+        <v>20771</v>
       </c>
       <c r="C73" t="n">
-        <v>111.03</v>
+        <v>24.01</v>
       </c>
       <c r="D73" t="n">
-        <v>26363</v>
+        <v>14841</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>90.42</v>
+        <v>26.11</v>
       </c>
       <c r="B74" t="n">
-        <v>23561</v>
+        <v>21425</v>
       </c>
       <c r="C74" t="n">
-        <v>91.22</v>
+        <v>24.16</v>
       </c>
       <c r="D74" t="n">
-        <v>26991</v>
+        <v>25755</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>114.75</v>
+        <v>26.31</v>
       </c>
       <c r="B75" t="n">
-        <v>25056</v>
+        <v>22986</v>
       </c>
       <c r="C75" t="n">
-        <v>116.55</v>
+        <v>26.6</v>
       </c>
       <c r="D75" t="n">
-        <v>22900</v>
+        <v>25977</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>9.07</v>
+        <v>26.85</v>
       </c>
       <c r="B76" t="n">
-        <v>25205</v>
+        <v>23911</v>
       </c>
       <c r="C76" t="n">
-        <v>8.380000000000001</v>
+        <v>28.57</v>
       </c>
       <c r="D76" t="n">
-        <v>18322</v>
+        <v>11984</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>91.42</v>
+        <v>27.08</v>
       </c>
       <c r="B77" t="n">
-        <v>23916</v>
+        <v>21409</v>
       </c>
       <c r="C77" t="n">
-        <v>93.72</v>
+        <v>30.02</v>
       </c>
       <c r="D77" t="n">
-        <v>25649</v>
+        <v>18505</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>96.36</v>
+        <v>27.31</v>
       </c>
       <c r="B78" t="n">
-        <v>38131</v>
+        <v>22696</v>
       </c>
       <c r="C78" t="n">
-        <v>93.69</v>
+        <v>35.93</v>
       </c>
       <c r="D78" t="n">
-        <v>25279</v>
+        <v>12046</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>50.41</v>
+        <v>27.55</v>
       </c>
       <c r="B79" t="n">
-        <v>23278</v>
+        <v>22989</v>
       </c>
       <c r="C79" t="n">
-        <v>49.33</v>
+        <v>30.13</v>
       </c>
       <c r="D79" t="n">
-        <v>13308</v>
+        <v>14111</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>91.88</v>
+        <v>28.68</v>
       </c>
       <c r="B80" t="n">
-        <v>25910</v>
+        <v>21390</v>
       </c>
       <c r="C80" t="n">
-        <v>90.53</v>
+        <v>23.21</v>
       </c>
       <c r="D80" t="n">
-        <v>25753</v>
+        <v>12753</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>97.55</v>
+        <v>29.07</v>
       </c>
       <c r="B81" t="n">
-        <v>36800</v>
+        <v>22272</v>
       </c>
       <c r="C81" t="n">
-        <v>97.51000000000001</v>
+        <v>35.69</v>
       </c>
       <c r="D81" t="n">
-        <v>15796</v>
+        <v>23794</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>106.4</v>
+        <v>29.22</v>
       </c>
       <c r="B82" t="n">
-        <v>42071</v>
+        <v>23622</v>
       </c>
       <c r="C82" t="n">
-        <v>106.42</v>
+        <v>17.44</v>
       </c>
       <c r="D82" t="n">
-        <v>15255</v>
+        <v>19756</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>90.69</v>
+        <v>29.34</v>
       </c>
       <c r="B83" t="n">
-        <v>24285</v>
+        <v>22049</v>
       </c>
       <c r="C83" t="n">
-        <v>91.69</v>
+        <v>26.33</v>
       </c>
       <c r="D83" t="n">
-        <v>29035</v>
+        <v>26651</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>24.63</v>
+        <v>29.89</v>
       </c>
       <c r="B84" t="n">
-        <v>23936</v>
+        <v>22288</v>
       </c>
       <c r="C84" t="n">
-        <v>24.16</v>
+        <v>30.95</v>
       </c>
       <c r="D84" t="n">
-        <v>23519</v>
+        <v>22578</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>114.37</v>
+        <v>30.31</v>
       </c>
       <c r="B85" t="n">
-        <v>22581</v>
+        <v>21778</v>
       </c>
       <c r="C85" t="n">
-        <v>114.71</v>
+        <v>22.94</v>
       </c>
       <c r="D85" t="n">
-        <v>13857</v>
+        <v>15264</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>140.24</v>
+        <v>30.65</v>
       </c>
       <c r="B86" t="n">
-        <v>22977</v>
+        <v>20403</v>
       </c>
       <c r="C86" t="n">
-        <v>143.33</v>
+        <v>28.53</v>
       </c>
       <c r="D86" t="n">
-        <v>13319</v>
+        <v>15525</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>8.16</v>
+        <v>30.69</v>
       </c>
       <c r="B87" t="n">
-        <v>23405</v>
+        <v>25277</v>
       </c>
       <c r="C87" t="n">
-        <v>8.220000000000001</v>
+        <v>41.4</v>
       </c>
       <c r="D87" t="n">
-        <v>29097</v>
+        <v>25199</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>90.95999999999999</v>
+        <v>32.98</v>
       </c>
       <c r="B88" t="n">
-        <v>24902</v>
+        <v>22623</v>
       </c>
       <c r="C88" t="n">
-        <v>88.43000000000001</v>
+        <v>30.1</v>
       </c>
       <c r="D88" t="n">
-        <v>26487</v>
+        <v>27486</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>90.56</v>
+        <v>33.25</v>
       </c>
       <c r="B89" t="n">
-        <v>24730</v>
+        <v>22717</v>
       </c>
       <c r="C89" t="n">
-        <v>87.64</v>
+        <v>35.05</v>
       </c>
       <c r="D89" t="n">
-        <v>23531</v>
+        <v>11937</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120.95</v>
+        <v>33.37</v>
       </c>
       <c r="B90" t="n">
-        <v>26311</v>
+        <v>23121</v>
       </c>
       <c r="C90" t="n">
-        <v>123.4</v>
+        <v>42.98</v>
       </c>
       <c r="D90" t="n">
-        <v>11475</v>
+        <v>20063</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>96.69</v>
+        <v>34.28</v>
       </c>
       <c r="B91" t="n">
-        <v>38136</v>
+        <v>20162</v>
       </c>
       <c r="C91" t="n">
-        <v>93.45</v>
+        <v>37.69</v>
       </c>
       <c r="D91" t="n">
-        <v>12822</v>
+        <v>16103</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131.84</v>
+        <v>34.95</v>
       </c>
       <c r="B92" t="n">
-        <v>23986</v>
+        <v>23325</v>
       </c>
       <c r="C92" t="n">
-        <v>131.84</v>
+        <v>43.5</v>
       </c>
       <c r="D92" t="n">
-        <v>12238</v>
+        <v>10552</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>102.97</v>
+        <v>34.96</v>
       </c>
       <c r="B93" t="n">
-        <v>47801</v>
+        <v>22190</v>
       </c>
       <c r="C93" t="n">
-        <v>104.02</v>
+        <v>33.03</v>
       </c>
       <c r="D93" t="n">
-        <v>22867</v>
+        <v>15524</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>96.94</v>
+        <v>35.51</v>
       </c>
       <c r="B94" t="n">
-        <v>37381</v>
+        <v>21214</v>
       </c>
       <c r="C94" t="n">
-        <v>96.34999999999999</v>
+        <v>46.3</v>
       </c>
       <c r="D94" t="n">
-        <v>12881</v>
+        <v>13045</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>113.01</v>
+        <v>36.64</v>
       </c>
       <c r="B95" t="n">
-        <v>26378</v>
+        <v>20057</v>
       </c>
       <c r="C95" t="n">
-        <v>112.87</v>
+        <v>41.27</v>
       </c>
       <c r="D95" t="n">
-        <v>26407</v>
+        <v>29533</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>100.96</v>
+        <v>36.85</v>
       </c>
       <c r="B96" t="n">
-        <v>45951</v>
+        <v>22736</v>
       </c>
       <c r="C96" t="n">
-        <v>101.28</v>
+        <v>34.64</v>
       </c>
       <c r="D96" t="n">
-        <v>18569</v>
+        <v>16443</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>111.64</v>
+        <v>36.91</v>
       </c>
       <c r="B97" t="n">
-        <v>30646</v>
+        <v>22545</v>
       </c>
       <c r="C97" t="n">
-        <v>114.54</v>
+        <v>37.81</v>
       </c>
       <c r="D97" t="n">
-        <v>22794</v>
+        <v>10162</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>98.51000000000001</v>
+        <v>37.23</v>
       </c>
       <c r="B98" t="n">
-        <v>40190</v>
+        <v>23644</v>
       </c>
       <c r="C98" t="n">
-        <v>99.13</v>
+        <v>36.24</v>
       </c>
       <c r="D98" t="n">
-        <v>12684</v>
+        <v>24330</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>92.81</v>
+        <v>37.32</v>
       </c>
       <c r="B99" t="n">
-        <v>25709</v>
+        <v>20289</v>
       </c>
       <c r="C99" t="n">
-        <v>94.65000000000001</v>
+        <v>44.53</v>
       </c>
       <c r="D99" t="n">
-        <v>11080</v>
+        <v>18295</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>60.99</v>
+        <v>38.05</v>
       </c>
       <c r="B100" t="n">
-        <v>23738</v>
+        <v>21583</v>
       </c>
       <c r="C100" t="n">
-        <v>63.34</v>
+        <v>37.57</v>
       </c>
       <c r="D100" t="n">
-        <v>12477</v>
+        <v>27760</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>102.82</v>
+        <v>38.7</v>
       </c>
       <c r="B101" t="n">
-        <v>46163</v>
+        <v>20819</v>
       </c>
       <c r="C101" t="n">
-        <v>102.02</v>
+        <v>43.53</v>
       </c>
       <c r="D101" t="n">
-        <v>21733</v>
+        <v>15061</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>113.26</v>
+        <v>38.72</v>
       </c>
       <c r="B102" t="n">
-        <v>24618</v>
+        <v>19935</v>
       </c>
       <c r="C102" t="n">
-        <v>115.85</v>
+        <v>45.35</v>
       </c>
       <c r="D102" t="n">
-        <v>11441</v>
+        <v>17265</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>92.23</v>
+        <v>38.84</v>
       </c>
       <c r="B103" t="n">
-        <v>28264</v>
+        <v>23491</v>
       </c>
       <c r="C103" t="n">
-        <v>88.56</v>
+        <v>40.59</v>
       </c>
       <c r="D103" t="n">
-        <v>18030</v>
+        <v>12420</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>111.14</v>
+        <v>38.85</v>
       </c>
       <c r="B104" t="n">
-        <v>29825</v>
+        <v>21391</v>
       </c>
       <c r="C104" t="n">
-        <v>112.18</v>
+        <v>24.05</v>
       </c>
       <c r="D104" t="n">
-        <v>24494</v>
+        <v>19374</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>108.87</v>
+        <v>39.09</v>
       </c>
       <c r="B105" t="n">
-        <v>34499</v>
+        <v>22684</v>
       </c>
       <c r="C105" t="n">
-        <v>110.86</v>
+        <v>31.79</v>
       </c>
       <c r="D105" t="n">
-        <v>15901</v>
+        <v>19774</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>94.5</v>
+        <v>40.84</v>
       </c>
       <c r="B106" t="n">
-        <v>34715</v>
+        <v>21706</v>
       </c>
       <c r="C106" t="n">
-        <v>94.59</v>
+        <v>40.33</v>
       </c>
       <c r="D106" t="n">
-        <v>23076</v>
+        <v>22190</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>91.38</v>
+        <v>40.87</v>
       </c>
       <c r="B107" t="n">
-        <v>23745</v>
+        <v>23287</v>
       </c>
       <c r="C107" t="n">
-        <v>90.14</v>
+        <v>48.81</v>
       </c>
       <c r="D107" t="n">
-        <v>11047</v>
+        <v>24474</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>91.20999999999999</v>
+        <v>41.46</v>
       </c>
       <c r="B108" t="n">
-        <v>25504</v>
+        <v>17511</v>
       </c>
       <c r="C108" t="n">
-        <v>89.75</v>
+        <v>38.68</v>
       </c>
       <c r="D108" t="n">
-        <v>28240</v>
+        <v>24217</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>106.88</v>
+        <v>41.79</v>
       </c>
       <c r="B109" t="n">
-        <v>40266</v>
+        <v>22127</v>
       </c>
       <c r="C109" t="n">
-        <v>110</v>
+        <v>46.03</v>
       </c>
       <c r="D109" t="n">
-        <v>20060</v>
+        <v>24366</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>109.91</v>
+        <v>42.16</v>
       </c>
       <c r="B110" t="n">
-        <v>33991</v>
+        <v>21751</v>
       </c>
       <c r="C110" t="n">
-        <v>113.17</v>
+        <v>36.74</v>
       </c>
       <c r="D110" t="n">
-        <v>15854</v>
+        <v>27184</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>97.51000000000001</v>
+        <v>42.42</v>
       </c>
       <c r="B111" t="n">
-        <v>37359</v>
+        <v>22048</v>
       </c>
       <c r="C111" t="n">
-        <v>97.59999999999999</v>
+        <v>37.17</v>
       </c>
       <c r="D111" t="n">
-        <v>24819</v>
+        <v>10794</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>114.03</v>
+        <v>43.2</v>
       </c>
       <c r="B112" t="n">
-        <v>21037</v>
+        <v>22892</v>
       </c>
       <c r="C112" t="n">
-        <v>110.38</v>
+        <v>43.18</v>
       </c>
       <c r="D112" t="n">
-        <v>22525</v>
+        <v>27644</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>144.72</v>
+        <v>43.77</v>
       </c>
       <c r="B113" t="n">
-        <v>22786</v>
+        <v>20778</v>
       </c>
       <c r="C113" t="n">
-        <v>143.1</v>
+        <v>32.94</v>
       </c>
       <c r="D113" t="n">
-        <v>22342</v>
+        <v>14533</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>93.44</v>
+        <v>43.98</v>
       </c>
       <c r="B114" t="n">
-        <v>29942</v>
+        <v>20630</v>
       </c>
       <c r="C114" t="n">
-        <v>94.16</v>
+        <v>42.31</v>
       </c>
       <c r="D114" t="n">
-        <v>13354</v>
+        <v>19341</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>93.55</v>
+        <v>44.13</v>
       </c>
       <c r="B115" t="n">
-        <v>28785</v>
+        <v>21802</v>
       </c>
       <c r="C115" t="n">
-        <v>89.03</v>
+        <v>50.27</v>
       </c>
       <c r="D115" t="n">
-        <v>29816</v>
+        <v>21758</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>65.94</v>
+        <v>44.14</v>
       </c>
       <c r="B116" t="n">
-        <v>22354</v>
+        <v>21323</v>
       </c>
       <c r="C116" t="n">
-        <v>67.73</v>
+        <v>48.95</v>
       </c>
       <c r="D116" t="n">
-        <v>26765</v>
+        <v>16553</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>104.79</v>
+        <v>44.22</v>
       </c>
       <c r="B117" t="n">
-        <v>44771</v>
+        <v>21098</v>
       </c>
       <c r="C117" t="n">
-        <v>109.83</v>
+        <v>49.05</v>
       </c>
       <c r="D117" t="n">
-        <v>16139</v>
+        <v>26603</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>27.43</v>
+        <v>44.66</v>
       </c>
       <c r="B118" t="n">
-        <v>22863</v>
+        <v>21819</v>
       </c>
       <c r="C118" t="n">
-        <v>27.26</v>
+        <v>37.8</v>
       </c>
       <c r="D118" t="n">
-        <v>22054</v>
+        <v>21533</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>98.15000000000001</v>
+        <v>44.74</v>
       </c>
       <c r="B119" t="n">
-        <v>42528</v>
+        <v>20069</v>
       </c>
       <c r="C119" t="n">
-        <v>101.72</v>
+        <v>44.46</v>
       </c>
       <c r="D119" t="n">
-        <v>18653</v>
+        <v>14689</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>107.02</v>
+        <v>44.75</v>
       </c>
       <c r="B120" t="n">
-        <v>42237</v>
+        <v>19869</v>
       </c>
       <c r="C120" t="n">
-        <v>107.6</v>
+        <v>52.64</v>
       </c>
       <c r="D120" t="n">
-        <v>22692</v>
+        <v>29733</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>103.12</v>
+        <v>45.55</v>
       </c>
       <c r="B121" t="n">
-        <v>46560</v>
+        <v>19912</v>
       </c>
       <c r="C121" t="n">
-        <v>100.23</v>
+        <v>42.38</v>
       </c>
       <c r="D121" t="n">
-        <v>17842</v>
+        <v>27807</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>93.38</v>
+        <v>45.81</v>
       </c>
       <c r="B122" t="n">
-        <v>31359</v>
+        <v>22474</v>
       </c>
       <c r="C122" t="n">
-        <v>93.20999999999999</v>
+        <v>42.83</v>
       </c>
       <c r="D122" t="n">
-        <v>20208</v>
+        <v>20906</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>103.83</v>
+        <v>47.54</v>
       </c>
       <c r="B123" t="n">
-        <v>48747</v>
+        <v>19858</v>
       </c>
       <c r="C123" t="n">
-        <v>100.34</v>
+        <v>60.25</v>
       </c>
       <c r="D123" t="n">
-        <v>16733</v>
+        <v>15575</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>104.04</v>
+        <v>47.55</v>
       </c>
       <c r="B124" t="n">
-        <v>47303</v>
+        <v>20374</v>
       </c>
       <c r="C124" t="n">
-        <v>106.12</v>
+        <v>35.45</v>
       </c>
       <c r="D124" t="n">
-        <v>15032</v>
+        <v>26107</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>69.25</v>
+        <v>47.79</v>
       </c>
       <c r="B125" t="n">
-        <v>22574</v>
+        <v>20839</v>
       </c>
       <c r="C125" t="n">
-        <v>67.95999999999999</v>
+        <v>45.88</v>
       </c>
       <c r="D125" t="n">
-        <v>13230</v>
+        <v>20293</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>111.79</v>
+        <v>48.7</v>
       </c>
       <c r="B126" t="n">
-        <v>30406</v>
+        <v>20483</v>
       </c>
       <c r="C126" t="n">
-        <v>109.39</v>
+        <v>45.12</v>
       </c>
       <c r="D126" t="n">
-        <v>23290</v>
+        <v>16091</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>96.20999999999999</v>
+        <v>48.76</v>
       </c>
       <c r="B127" t="n">
-        <v>38244</v>
+        <v>19103</v>
       </c>
       <c r="C127" t="n">
-        <v>99.3</v>
+        <v>51.57</v>
       </c>
       <c r="D127" t="n">
-        <v>12847</v>
+        <v>10806</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>106.8</v>
+        <v>48.95</v>
       </c>
       <c r="B128" t="n">
-        <v>44398</v>
+        <v>19360</v>
       </c>
       <c r="C128" t="n">
-        <v>102.6</v>
+        <v>55.27</v>
       </c>
       <c r="D128" t="n">
-        <v>11475</v>
+        <v>11490</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>90.38</v>
+        <v>49.66</v>
       </c>
       <c r="B129" t="n">
-        <v>22699</v>
+        <v>20507</v>
       </c>
       <c r="C129" t="n">
-        <v>91.17</v>
+        <v>45.16</v>
       </c>
       <c r="D129" t="n">
-        <v>17942</v>
+        <v>15620</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>101.42</v>
+        <v>49.8</v>
       </c>
       <c r="B130" t="n">
-        <v>46001</v>
+        <v>21366</v>
       </c>
       <c r="C130" t="n">
-        <v>101.15</v>
+        <v>52.13</v>
       </c>
       <c r="D130" t="n">
-        <v>12562</v>
+        <v>24055</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>97.70999999999999</v>
+        <v>50.3</v>
       </c>
       <c r="B131" t="n">
-        <v>40793</v>
+        <v>23609</v>
       </c>
       <c r="C131" t="n">
-        <v>96.55</v>
+        <v>58.39</v>
       </c>
       <c r="D131" t="n">
-        <v>25827</v>
+        <v>29671</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>64.86</v>
+        <v>50.81</v>
       </c>
       <c r="B132" t="n">
-        <v>25796</v>
+        <v>21014</v>
       </c>
       <c r="C132" t="n">
-        <v>66.04000000000001</v>
+        <v>45.23</v>
       </c>
       <c r="D132" t="n">
-        <v>21131</v>
+        <v>12050</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>91.63</v>
+        <v>52.37</v>
       </c>
       <c r="B133" t="n">
-        <v>23618</v>
+        <v>20942</v>
       </c>
       <c r="C133" t="n">
-        <v>94.75</v>
+        <v>65.86</v>
       </c>
       <c r="D133" t="n">
-        <v>13787</v>
+        <v>10385</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>106.85</v>
+        <v>52.69</v>
       </c>
       <c r="B134" t="n">
-        <v>42584</v>
+        <v>21153</v>
       </c>
       <c r="C134" t="n">
-        <v>105.6</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="D134" t="n">
-        <v>22319</v>
+        <v>25817</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>107.58</v>
+        <v>52.85</v>
       </c>
       <c r="B135" t="n">
-        <v>39644</v>
+        <v>20310</v>
       </c>
       <c r="C135" t="n">
-        <v>112.02</v>
+        <v>49.82</v>
       </c>
       <c r="D135" t="n">
-        <v>20151</v>
+        <v>27550</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>156.41</v>
+        <v>53.29</v>
       </c>
       <c r="B136" t="n">
-        <v>22456</v>
+        <v>22186</v>
       </c>
       <c r="C136" t="n">
-        <v>155.56</v>
+        <v>59.05</v>
       </c>
       <c r="D136" t="n">
-        <v>22233</v>
+        <v>20690</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>104.91</v>
+        <v>53.37</v>
       </c>
       <c r="B137" t="n">
-        <v>42363</v>
+        <v>20963</v>
       </c>
       <c r="C137" t="n">
-        <v>101.56</v>
+        <v>57.9</v>
       </c>
       <c r="D137" t="n">
-        <v>18656</v>
+        <v>17581</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>41.02</v>
+        <v>53.57</v>
       </c>
       <c r="B138" t="n">
-        <v>26007</v>
+        <v>16928</v>
       </c>
       <c r="C138" t="n">
-        <v>42.17</v>
+        <v>50.77</v>
       </c>
       <c r="D138" t="n">
-        <v>28790</v>
+        <v>16453</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135.64</v>
+        <v>53.63</v>
       </c>
       <c r="B139" t="n">
-        <v>26061</v>
+        <v>22786</v>
       </c>
       <c r="C139" t="n">
-        <v>139.64</v>
+        <v>49.87</v>
       </c>
       <c r="D139" t="n">
-        <v>20036</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>148.7</v>
+        <v>53.65</v>
       </c>
       <c r="B140" t="n">
-        <v>22671</v>
+        <v>22241</v>
       </c>
       <c r="C140" t="n">
-        <v>145.37</v>
+        <v>39.14</v>
       </c>
       <c r="D140" t="n">
-        <v>12228</v>
+        <v>26755</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>112.14</v>
+        <v>54.58</v>
       </c>
       <c r="B141" t="n">
-        <v>27959</v>
+        <v>20316</v>
       </c>
       <c r="C141" t="n">
-        <v>115.35</v>
+        <v>53.18</v>
       </c>
       <c r="D141" t="n">
-        <v>24744</v>
+        <v>23884</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>111.55</v>
+        <v>54.77</v>
       </c>
       <c r="B142" t="n">
-        <v>28692</v>
+        <v>20419</v>
       </c>
       <c r="C142" t="n">
-        <v>109.09</v>
+        <v>40.9</v>
       </c>
       <c r="D142" t="n">
-        <v>21708</v>
+        <v>18317</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>98.83</v>
+        <v>56.27</v>
       </c>
       <c r="B143" t="n">
-        <v>39764</v>
+        <v>19091</v>
       </c>
       <c r="C143" t="n">
-        <v>101.85</v>
+        <v>65.05</v>
       </c>
       <c r="D143" t="n">
-        <v>19021</v>
+        <v>13601</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>113.26</v>
+        <v>56.65</v>
       </c>
       <c r="B144" t="n">
-        <v>26647</v>
+        <v>20867</v>
       </c>
       <c r="C144" t="n">
-        <v>113.18</v>
+        <v>52.68</v>
       </c>
       <c r="D144" t="n">
-        <v>14461</v>
+        <v>14924</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>94.68000000000001</v>
+        <v>57.76</v>
       </c>
       <c r="B145" t="n">
-        <v>32343</v>
+        <v>21554</v>
       </c>
       <c r="C145" t="n">
-        <v>92</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="D145" t="n">
-        <v>12188</v>
+        <v>11623</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>92.84999999999999</v>
+        <v>58.01</v>
       </c>
       <c r="B146" t="n">
-        <v>29537</v>
+        <v>18817</v>
       </c>
       <c r="C146" t="n">
-        <v>89.59</v>
+        <v>43.86</v>
       </c>
       <c r="D146" t="n">
-        <v>28868</v>
+        <v>13802</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>103.46</v>
+        <v>58.27</v>
       </c>
       <c r="B147" t="n">
-        <v>45532</v>
+        <v>20631</v>
       </c>
       <c r="C147" t="n">
-        <v>102.55</v>
+        <v>52.28</v>
       </c>
       <c r="D147" t="n">
-        <v>12657</v>
+        <v>15545</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>113.61</v>
+        <v>58.89</v>
       </c>
       <c r="B148" t="n">
-        <v>23703</v>
+        <v>19898</v>
       </c>
       <c r="C148" t="n">
-        <v>118.15</v>
+        <v>62.79</v>
       </c>
       <c r="D148" t="n">
-        <v>28369</v>
+        <v>22189</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>103.51</v>
+        <v>59.29</v>
       </c>
       <c r="B149" t="n">
-        <v>45115</v>
+        <v>22194</v>
       </c>
       <c r="C149" t="n">
-        <v>105.28</v>
+        <v>58.47</v>
       </c>
       <c r="D149" t="n">
-        <v>15671</v>
+        <v>11436</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>102.91</v>
+        <v>60.67</v>
       </c>
       <c r="B150" t="n">
-        <v>44941</v>
+        <v>20826</v>
       </c>
       <c r="C150" t="n">
-        <v>105.65</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="D150" t="n">
-        <v>21103</v>
+        <v>16318</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>99.04000000000001</v>
+        <v>60.67</v>
       </c>
       <c r="B151" t="n">
-        <v>43349</v>
+        <v>21768</v>
       </c>
       <c r="C151" t="n">
-        <v>100.21</v>
+        <v>66.05</v>
       </c>
       <c r="D151" t="n">
-        <v>13315</v>
+        <v>19011</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>51.82</v>
+        <v>60.95</v>
       </c>
       <c r="B152" t="n">
-        <v>21309</v>
+        <v>20145</v>
       </c>
       <c r="C152" t="n">
-        <v>50.39</v>
+        <v>65.23</v>
       </c>
       <c r="D152" t="n">
-        <v>13813</v>
+        <v>24617</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>95.37</v>
+        <v>61.4</v>
       </c>
       <c r="B153" t="n">
-        <v>34090</v>
+        <v>20594</v>
       </c>
       <c r="C153" t="n">
-        <v>92.72</v>
+        <v>55.18</v>
       </c>
       <c r="D153" t="n">
-        <v>28130</v>
+        <v>16355</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>111.71</v>
+        <v>61.48</v>
       </c>
       <c r="B154" t="n">
-        <v>24776</v>
+        <v>21504</v>
       </c>
       <c r="C154" t="n">
-        <v>111.09</v>
+        <v>75.84</v>
       </c>
       <c r="D154" t="n">
-        <v>14000</v>
+        <v>12747</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>90.95</v>
+        <v>61.66</v>
       </c>
       <c r="B155" t="n">
-        <v>24843</v>
+        <v>21600</v>
       </c>
       <c r="C155" t="n">
-        <v>89.17</v>
+        <v>66.72</v>
       </c>
       <c r="D155" t="n">
-        <v>21699</v>
+        <v>27728</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>108.04</v>
+        <v>62.43</v>
       </c>
       <c r="B156" t="n">
-        <v>36136</v>
+        <v>20006</v>
       </c>
       <c r="C156" t="n">
-        <v>106.01</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="D156" t="n">
-        <v>20246</v>
+        <v>15726</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>95.98999999999999</v>
+        <v>62.43</v>
       </c>
       <c r="B157" t="n">
-        <v>36380</v>
+        <v>20946</v>
       </c>
       <c r="C157" t="n">
-        <v>98.86</v>
+        <v>54.6</v>
       </c>
       <c r="D157" t="n">
-        <v>26920</v>
+        <v>10692</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>111.28</v>
+        <v>62.45</v>
       </c>
       <c r="B158" t="n">
-        <v>28064</v>
+        <v>20666</v>
       </c>
       <c r="C158" t="n">
-        <v>111.32</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="D158" t="n">
-        <v>13481</v>
+        <v>26977</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>97.2</v>
+        <v>62.79</v>
       </c>
       <c r="B159" t="n">
-        <v>41477</v>
+        <v>20744</v>
       </c>
       <c r="C159" t="n">
-        <v>98.58</v>
+        <v>54.14</v>
       </c>
       <c r="D159" t="n">
-        <v>11408</v>
+        <v>15628</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>108.99</v>
+        <v>63.26</v>
       </c>
       <c r="B160" t="n">
-        <v>35259</v>
+        <v>21598</v>
       </c>
       <c r="C160" t="n">
-        <v>111.66</v>
+        <v>61.62</v>
       </c>
       <c r="D160" t="n">
-        <v>18379</v>
+        <v>23763</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>113.99</v>
+        <v>63.38</v>
       </c>
       <c r="B161" t="n">
-        <v>22757</v>
+        <v>22217</v>
       </c>
       <c r="C161" t="n">
-        <v>112.94</v>
+        <v>73.28</v>
       </c>
       <c r="D161" t="n">
-        <v>17420</v>
+        <v>19205</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>100.19</v>
+        <v>63.8</v>
       </c>
       <c r="B162" t="n">
-        <v>44452</v>
+        <v>20523</v>
       </c>
       <c r="C162" t="n">
-        <v>103.98</v>
+        <v>76.45</v>
       </c>
       <c r="D162" t="n">
-        <v>13484</v>
+        <v>21048</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>100.18</v>
+        <v>63.97</v>
       </c>
       <c r="B163" t="n">
-        <v>42380</v>
+        <v>21012</v>
       </c>
       <c r="C163" t="n">
-        <v>97.59</v>
+        <v>63.94</v>
       </c>
       <c r="D163" t="n">
-        <v>26516</v>
+        <v>11487</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>93.31</v>
+        <v>64</v>
       </c>
       <c r="B164" t="n">
-        <v>29600</v>
+        <v>20483</v>
       </c>
       <c r="C164" t="n">
-        <v>92.36</v>
+        <v>59.12</v>
       </c>
       <c r="D164" t="n">
-        <v>18911</v>
+        <v>20329</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>106.2</v>
+        <v>65.34</v>
       </c>
       <c r="B165" t="n">
-        <v>41453</v>
+        <v>20370</v>
       </c>
       <c r="C165" t="n">
-        <v>105.07</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="D165" t="n">
-        <v>15118</v>
+        <v>25967</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>101.95</v>
+        <v>65.86</v>
       </c>
       <c r="B166" t="n">
-        <v>45631</v>
+        <v>19700</v>
       </c>
       <c r="C166" t="n">
-        <v>104.47</v>
+        <v>53.49</v>
       </c>
       <c r="D166" t="n">
-        <v>18736</v>
+        <v>23507</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>100.75</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="B167" t="n">
-        <v>43528</v>
+        <v>21254</v>
       </c>
       <c r="C167" t="n">
-        <v>103.48</v>
+        <v>55.66</v>
       </c>
       <c r="D167" t="n">
-        <v>26462</v>
+        <v>22047</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>106.93</v>
+        <v>66.36</v>
       </c>
       <c r="B168" t="n">
-        <v>45706</v>
+        <v>20576</v>
       </c>
       <c r="C168" t="n">
-        <v>106.33</v>
+        <v>60.55</v>
       </c>
       <c r="D168" t="n">
-        <v>15717</v>
+        <v>23251</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>91.51000000000001</v>
+        <v>66.45</v>
       </c>
       <c r="B169" t="n">
-        <v>25683</v>
+        <v>22380</v>
       </c>
       <c r="C169" t="n">
-        <v>95.25</v>
+        <v>78.2</v>
       </c>
       <c r="D169" t="n">
-        <v>15930</v>
+        <v>18023</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>108.11</v>
+        <v>66.61</v>
       </c>
       <c r="B170" t="n">
-        <v>38419</v>
+        <v>20518</v>
       </c>
       <c r="C170" t="n">
-        <v>109.52</v>
+        <v>62.54</v>
       </c>
       <c r="D170" t="n">
-        <v>12162</v>
+        <v>29216</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>101.52</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="B171" t="n">
-        <v>45902</v>
+        <v>21834</v>
       </c>
       <c r="C171" t="n">
-        <v>100.83</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="D171" t="n">
-        <v>27628</v>
+        <v>24123</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>104.94</v>
+        <v>66.81</v>
       </c>
       <c r="B172" t="n">
-        <v>45893</v>
+        <v>21039</v>
       </c>
       <c r="C172" t="n">
-        <v>103.18</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D172" t="n">
-        <v>13061</v>
+        <v>13486</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>106.96</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="B173" t="n">
-        <v>42949</v>
+        <v>21356</v>
       </c>
       <c r="C173" t="n">
-        <v>105.53</v>
+        <v>72.75</v>
       </c>
       <c r="D173" t="n">
-        <v>12637</v>
+        <v>24541</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>114.9</v>
+        <v>67.05</v>
       </c>
       <c r="B174" t="n">
-        <v>24007</v>
+        <v>21885</v>
       </c>
       <c r="C174" t="n">
-        <v>112.59</v>
+        <v>53.27</v>
       </c>
       <c r="D174" t="n">
-        <v>24729</v>
+        <v>15239</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>104.43</v>
+        <v>67.11</v>
       </c>
       <c r="B175" t="n">
-        <v>44556</v>
+        <v>19707</v>
       </c>
       <c r="C175" t="n">
-        <v>104.2</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="D175" t="n">
-        <v>28808</v>
+        <v>25918</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>92.65000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="B176" t="n">
-        <v>24488</v>
+        <v>20987</v>
       </c>
       <c r="C176" t="n">
-        <v>93.70999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="D176" t="n">
-        <v>13610</v>
+        <v>13300</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>95.47</v>
+        <v>67.55</v>
       </c>
       <c r="B177" t="n">
-        <v>35204</v>
+        <v>21068</v>
       </c>
       <c r="C177" t="n">
-        <v>95.13</v>
+        <v>61.86</v>
       </c>
       <c r="D177" t="n">
-        <v>28505</v>
+        <v>13915</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>105.2</v>
+        <v>68.5</v>
       </c>
       <c r="B178" t="n">
-        <v>44403</v>
+        <v>21081</v>
       </c>
       <c r="C178" t="n">
-        <v>104.78</v>
+        <v>65.23</v>
       </c>
       <c r="D178" t="n">
-        <v>23311</v>
+        <v>16306</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>102.97</v>
+        <v>68.77</v>
       </c>
       <c r="B179" t="n">
-        <v>45732</v>
+        <v>20305</v>
       </c>
       <c r="C179" t="n">
-        <v>99.95</v>
+        <v>73.48</v>
       </c>
       <c r="D179" t="n">
-        <v>11942</v>
+        <v>22114</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>105.23</v>
+        <v>69.25</v>
       </c>
       <c r="B180" t="n">
-        <v>44943</v>
+        <v>20647</v>
       </c>
       <c r="C180" t="n">
-        <v>101.69</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="D180" t="n">
-        <v>18868</v>
+        <v>18909</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>108.12</v>
+        <v>69.86</v>
       </c>
       <c r="B181" t="n">
-        <v>39717</v>
+        <v>21293</v>
       </c>
       <c r="C181" t="n">
-        <v>106.2</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D181" t="n">
-        <v>29477</v>
+        <v>22485</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>112.59</v>
+        <v>70.23</v>
       </c>
       <c r="B182" t="n">
-        <v>27407</v>
+        <v>18935</v>
       </c>
       <c r="C182" t="n">
-        <v>110.14</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="D182" t="n">
-        <v>21853</v>
+        <v>29805</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>103.82</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="B183" t="n">
-        <v>47111</v>
+        <v>20271</v>
       </c>
       <c r="C183" t="n">
-        <v>103.42</v>
+        <v>68.55</v>
       </c>
       <c r="D183" t="n">
-        <v>12605</v>
+        <v>12024</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>110.49</v>
+        <v>71.88</v>
       </c>
       <c r="B184" t="n">
-        <v>31761</v>
+        <v>20817</v>
       </c>
       <c r="C184" t="n">
-        <v>111.85</v>
+        <v>59.67</v>
       </c>
       <c r="D184" t="n">
-        <v>16453</v>
+        <v>13467</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>99.25</v>
+        <v>72.14</v>
       </c>
       <c r="B185" t="n">
-        <v>43832</v>
+        <v>20959</v>
       </c>
       <c r="C185" t="n">
-        <v>97.59</v>
+        <v>72.05</v>
       </c>
       <c r="D185" t="n">
-        <v>21946</v>
+        <v>10365</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>100.2</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="B186" t="n">
-        <v>43330</v>
+        <v>21286</v>
       </c>
       <c r="C186" t="n">
-        <v>96.54000000000001</v>
+        <v>62.77</v>
       </c>
       <c r="D186" t="n">
-        <v>26946</v>
+        <v>23490</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>114.42</v>
+        <v>73.33</v>
       </c>
       <c r="B187" t="n">
-        <v>22729</v>
+        <v>20581</v>
       </c>
       <c r="C187" t="n">
-        <v>112.13</v>
+        <v>61.99</v>
       </c>
       <c r="D187" t="n">
-        <v>18718</v>
+        <v>16004</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>109.3</v>
+        <v>73.36</v>
       </c>
       <c r="B188" t="n">
-        <v>35917</v>
+        <v>21015</v>
       </c>
       <c r="C188" t="n">
-        <v>109.79</v>
+        <v>74.36</v>
       </c>
       <c r="D188" t="n">
-        <v>19129</v>
+        <v>21932</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>93.86</v>
+        <v>73.63</v>
       </c>
       <c r="B189" t="n">
-        <v>34643</v>
+        <v>20493</v>
       </c>
       <c r="C189" t="n">
-        <v>96.97</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="D189" t="n">
-        <v>12036</v>
+        <v>20707</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>111.68</v>
+        <v>74.08</v>
       </c>
       <c r="B190" t="n">
-        <v>26779</v>
+        <v>19592</v>
       </c>
       <c r="C190" t="n">
-        <v>115.2</v>
+        <v>84.98</v>
       </c>
       <c r="D190" t="n">
-        <v>21884</v>
+        <v>20070</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>97.11</v>
+        <v>74.37</v>
       </c>
       <c r="B191" t="n">
-        <v>36721</v>
+        <v>21076</v>
       </c>
       <c r="C191" t="n">
-        <v>95.98999999999999</v>
+        <v>66.42</v>
       </c>
       <c r="D191" t="n">
-        <v>26792</v>
+        <v>24706</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>93.64</v>
+        <v>74.69</v>
       </c>
       <c r="B192" t="n">
-        <v>28864</v>
+        <v>19984</v>
       </c>
       <c r="C192" t="n">
-        <v>96.55</v>
+        <v>81.7</v>
       </c>
       <c r="D192" t="n">
-        <v>11914</v>
+        <v>15232</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>114</v>
+        <v>74.92</v>
       </c>
       <c r="B193" t="n">
-        <v>25198</v>
+        <v>19451</v>
       </c>
       <c r="C193" t="n">
-        <v>115.65</v>
+        <v>71.08</v>
       </c>
       <c r="D193" t="n">
-        <v>17517</v>
+        <v>28398</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>100.45</v>
+        <v>74.97</v>
       </c>
       <c r="B194" t="n">
-        <v>45474</v>
+        <v>19835</v>
       </c>
       <c r="C194" t="n">
-        <v>97.81999999999999</v>
+        <v>92.77</v>
       </c>
       <c r="D194" t="n">
-        <v>12843</v>
+        <v>19527</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>103.37</v>
+        <v>75.16</v>
       </c>
       <c r="B195" t="n">
-        <v>47000</v>
+        <v>20161</v>
       </c>
       <c r="C195" t="n">
-        <v>99.17</v>
+        <v>84.17</v>
       </c>
       <c r="D195" t="n">
-        <v>11275</v>
+        <v>28915</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>111.4</v>
+        <v>75.5</v>
       </c>
       <c r="B196" t="n">
-        <v>27316</v>
+        <v>19883</v>
       </c>
       <c r="C196" t="n">
-        <v>115.32</v>
+        <v>79.86</v>
       </c>
       <c r="D196" t="n">
-        <v>25963</v>
+        <v>16866</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>112.33</v>
+        <v>76.34</v>
       </c>
       <c r="B197" t="n">
-        <v>28282</v>
+        <v>20706</v>
       </c>
       <c r="C197" t="n">
-        <v>112.37</v>
+        <v>84.55</v>
       </c>
       <c r="D197" t="n">
-        <v>14455</v>
+        <v>22866</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>101.53</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="B198" t="n">
-        <v>47146</v>
+        <v>20391</v>
       </c>
       <c r="C198" t="n">
-        <v>101.72</v>
+        <v>99.53</v>
       </c>
       <c r="D198" t="n">
-        <v>12390</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>111.05</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="B199" t="n">
-        <v>31278</v>
+        <v>19763</v>
       </c>
       <c r="C199" t="n">
-        <v>109.75</v>
+        <v>80.36</v>
       </c>
       <c r="D199" t="n">
-        <v>13521</v>
+        <v>20476</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>111.67</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="B200" t="n">
-        <v>28133</v>
+        <v>20821</v>
       </c>
       <c r="C200" t="n">
-        <v>109.86</v>
+        <v>60.27</v>
       </c>
       <c r="D200" t="n">
-        <v>16097</v>
+        <v>15545</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>94.40000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="B201" t="n">
-        <v>34533</v>
+        <v>20293</v>
       </c>
       <c r="C201" t="n">
-        <v>90.66</v>
+        <v>74.89</v>
       </c>
       <c r="D201" t="n">
-        <v>27731</v>
+        <v>15283</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>111.41</v>
+        <v>78.62</v>
       </c>
       <c r="B202" t="n">
-        <v>27995</v>
+        <v>20631</v>
       </c>
       <c r="C202" t="n">
-        <v>115.09</v>
+        <v>81.22</v>
       </c>
       <c r="D202" t="n">
-        <v>25013</v>
+        <v>12088</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>97.19</v>
+        <v>78.64</v>
       </c>
       <c r="B203" t="n">
-        <v>38484</v>
+        <v>20840</v>
       </c>
       <c r="C203" t="n">
-        <v>95.81999999999999</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="D203" t="n">
-        <v>20075</v>
+        <v>18609</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>149.26</v>
+        <v>78.7</v>
       </c>
       <c r="B204" t="n">
-        <v>23521</v>
+        <v>20499</v>
       </c>
       <c r="C204" t="n">
-        <v>152.89</v>
+        <v>85.13</v>
       </c>
       <c r="D204" t="n">
-        <v>16353</v>
+        <v>26653</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>103.62</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="B205" t="n">
-        <v>46094</v>
+        <v>20971</v>
       </c>
       <c r="C205" t="n">
-        <v>102.63</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="D205" t="n">
-        <v>23775</v>
+        <v>20929</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>107.85</v>
+        <v>79.37</v>
       </c>
       <c r="B206" t="n">
-        <v>39355</v>
+        <v>20584</v>
       </c>
       <c r="C206" t="n">
-        <v>112.43</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="D206" t="n">
-        <v>13677</v>
+        <v>27065</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>95.08</v>
+        <v>79.41</v>
       </c>
       <c r="B207" t="n">
-        <v>32299</v>
+        <v>21088</v>
       </c>
       <c r="C207" t="n">
-        <v>95.29000000000001</v>
+        <v>89.06</v>
       </c>
       <c r="D207" t="n">
-        <v>23887</v>
+        <v>19687</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>92.56999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="B208" t="n">
-        <v>27650</v>
+        <v>21067</v>
       </c>
       <c r="C208" t="n">
-        <v>95.06999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="D208" t="n">
-        <v>17616</v>
+        <v>19660</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>105.38</v>
+        <v>79.55</v>
       </c>
       <c r="B209" t="n">
-        <v>44419</v>
+        <v>19587</v>
       </c>
       <c r="C209" t="n">
-        <v>101.82</v>
+        <v>70.92</v>
       </c>
       <c r="D209" t="n">
-        <v>19094</v>
+        <v>25508</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>116.17</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="B210" t="n">
-        <v>21426</v>
+        <v>19937</v>
       </c>
       <c r="C210" t="n">
-        <v>119.12</v>
+        <v>66.66</v>
       </c>
       <c r="D210" t="n">
-        <v>23703</v>
+        <v>10422</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>110.97</v>
+        <v>80.25</v>
       </c>
       <c r="B211" t="n">
-        <v>28893</v>
+        <v>21123</v>
       </c>
       <c r="C211" t="n">
-        <v>108.2</v>
+        <v>91.13</v>
       </c>
       <c r="D211" t="n">
-        <v>11774</v>
+        <v>25084</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>102.32</v>
+        <v>80.56</v>
       </c>
       <c r="B212" t="n">
-        <v>45988</v>
+        <v>20335</v>
       </c>
       <c r="C212" t="n">
-        <v>102.03</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="D212" t="n">
-        <v>16989</v>
+        <v>23653</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>104.86</v>
+        <v>80.67</v>
       </c>
       <c r="B213" t="n">
-        <v>47330</v>
+        <v>20334</v>
       </c>
       <c r="C213" t="n">
-        <v>104.91</v>
+        <v>64.72</v>
       </c>
       <c r="D213" t="n">
-        <v>20593</v>
+        <v>28410</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>97.51000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="B214" t="n">
-        <v>40987</v>
+        <v>20020</v>
       </c>
       <c r="C214" t="n">
-        <v>97.31</v>
+        <v>74.92</v>
       </c>
       <c r="D214" t="n">
-        <v>16400</v>
+        <v>28340</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>98.93000000000001</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="B215" t="n">
-        <v>43287</v>
+        <v>20494</v>
       </c>
       <c r="C215" t="n">
-        <v>103.71</v>
+        <v>91.59</v>
       </c>
       <c r="D215" t="n">
-        <v>11785</v>
+        <v>22980</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>94.93000000000001</v>
+        <v>81.02</v>
       </c>
       <c r="B216" t="n">
-        <v>33926</v>
+        <v>19664</v>
       </c>
       <c r="C216" t="n">
-        <v>93.12</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="D216" t="n">
-        <v>16546</v>
+        <v>17944</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>97.52</v>
+        <v>81.14</v>
       </c>
       <c r="B217" t="n">
-        <v>41601</v>
+        <v>20046</v>
       </c>
       <c r="C217" t="n">
-        <v>95.42</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="D217" t="n">
-        <v>25993</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>103.25</v>
+        <v>81.89</v>
       </c>
       <c r="B218" t="n">
-        <v>47783</v>
+        <v>20373</v>
       </c>
       <c r="C218" t="n">
-        <v>101.55</v>
+        <v>78.88</v>
       </c>
       <c r="D218" t="n">
-        <v>24058</v>
+        <v>11367</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>100.23</v>
+        <v>82.83</v>
       </c>
       <c r="B219" t="n">
-        <v>45934</v>
+        <v>20206</v>
       </c>
       <c r="C219" t="n">
-        <v>97.73999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="D219" t="n">
-        <v>15768</v>
+        <v>29616</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>91.81</v>
+        <v>83.58</v>
       </c>
       <c r="B220" t="n">
-        <v>23175</v>
+        <v>20200</v>
       </c>
       <c r="C220" t="n">
-        <v>89.25</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D220" t="n">
-        <v>23105</v>
+        <v>16178</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>94.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="B221" t="n">
-        <v>33053</v>
+        <v>20101</v>
       </c>
       <c r="C221" t="n">
-        <v>91.47</v>
+        <v>91.91</v>
       </c>
       <c r="D221" t="n">
-        <v>18207</v>
+        <v>11385</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>90.56999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="B222" t="n">
-        <v>25082</v>
+        <v>21086</v>
       </c>
       <c r="C222" t="n">
-        <v>93.34</v>
+        <v>70.19</v>
       </c>
       <c r="D222" t="n">
-        <v>27813</v>
+        <v>11890</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>109.41</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="B223" t="n">
-        <v>33295</v>
+        <v>20623</v>
       </c>
       <c r="C223" t="n">
-        <v>111.14</v>
+        <v>96.3</v>
       </c>
       <c r="D223" t="n">
-        <v>24782</v>
+        <v>28969</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>103.83</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="B224" t="n">
-        <v>47125</v>
+        <v>20859</v>
       </c>
       <c r="C224" t="n">
-        <v>104.89</v>
+        <v>87.22</v>
       </c>
       <c r="D224" t="n">
-        <v>15170</v>
+        <v>28806</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>58.04</v>
+        <v>86.06</v>
       </c>
       <c r="B225" t="n">
-        <v>22814</v>
+        <v>19628</v>
       </c>
       <c r="C225" t="n">
-        <v>56.9</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="D225" t="n">
-        <v>13684</v>
+        <v>12935</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>90.78</v>
+        <v>86.91</v>
       </c>
       <c r="B226" t="n">
-        <v>25098</v>
+        <v>19435</v>
       </c>
       <c r="C226" t="n">
-        <v>93.45</v>
+        <v>84.22</v>
       </c>
       <c r="D226" t="n">
-        <v>13529</v>
+        <v>10909</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>95.56999999999999</v>
+        <v>87.33</v>
       </c>
       <c r="B227" t="n">
-        <v>36225</v>
+        <v>20802</v>
       </c>
       <c r="C227" t="n">
-        <v>95.39</v>
+        <v>79.91</v>
       </c>
       <c r="D227" t="n">
-        <v>23778</v>
+        <v>24005</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>114.56</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="B228" t="n">
-        <v>24293</v>
+        <v>20202</v>
       </c>
       <c r="C228" t="n">
-        <v>115.89</v>
+        <v>93.14</v>
       </c>
       <c r="D228" t="n">
-        <v>23563</v>
+        <v>28707</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>103.9</v>
+        <v>88.27</v>
       </c>
       <c r="B229" t="n">
-        <v>48068</v>
+        <v>21256</v>
       </c>
       <c r="C229" t="n">
-        <v>103.96</v>
+        <v>89.66</v>
       </c>
       <c r="D229" t="n">
-        <v>11482</v>
+        <v>29775</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>76.09999999999999</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="B230" t="n">
-        <v>23814</v>
+        <v>20988</v>
       </c>
       <c r="C230" t="n">
-        <v>74.88</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D230" t="n">
-        <v>25680</v>
+        <v>25594</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>110.28</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="B231" t="n">
-        <v>31066</v>
+        <v>21102</v>
       </c>
       <c r="C231" t="n">
-        <v>110.47</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="D231" t="n">
-        <v>20623</v>
+        <v>20561</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>97.13</v>
+        <v>89.37</v>
       </c>
       <c r="B232" t="n">
-        <v>38548</v>
+        <v>19883</v>
       </c>
       <c r="C232" t="n">
-        <v>94.31999999999999</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="D232" t="n">
-        <v>16547</v>
+        <v>26565</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>111.8</v>
+        <v>89.52</v>
       </c>
       <c r="B233" t="n">
-        <v>29354</v>
+        <v>21071</v>
       </c>
       <c r="C233" t="n">
-        <v>108.83</v>
+        <v>108.27</v>
       </c>
       <c r="D233" t="n">
-        <v>19375</v>
+        <v>27192</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>90.84999999999999</v>
+        <v>89.62</v>
       </c>
       <c r="B234" t="n">
-        <v>22440</v>
+        <v>20700</v>
       </c>
       <c r="C234" t="n">
-        <v>93.48</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="D234" t="n">
-        <v>22041</v>
+        <v>19264</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>104.14</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="B235" t="n">
-        <v>47993</v>
+        <v>19872</v>
       </c>
       <c r="C235" t="n">
-        <v>102.87</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="D235" t="n">
-        <v>13954</v>
+        <v>23415</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>112.9</v>
+        <v>89.87</v>
       </c>
       <c r="B236" t="n">
-        <v>24578</v>
+        <v>20127</v>
       </c>
       <c r="C236" t="n">
-        <v>109.01</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D236" t="n">
-        <v>13779</v>
+        <v>24510</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>88.75</v>
+        <v>90.11</v>
       </c>
       <c r="B237" t="n">
-        <v>22158</v>
+        <v>20368</v>
       </c>
       <c r="C237" t="n">
-        <v>90.12</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="D237" t="n">
-        <v>20690</v>
+        <v>14547</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>99.98999999999999</v>
+        <v>90.83</v>
       </c>
       <c r="B238" t="n">
-        <v>44517</v>
+        <v>22062</v>
       </c>
       <c r="C238" t="n">
-        <v>99.88</v>
+        <v>94.86</v>
       </c>
       <c r="D238" t="n">
-        <v>28303</v>
+        <v>21913</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>125.01</v>
+        <v>91.52</v>
       </c>
       <c r="B239" t="n">
-        <v>23989</v>
+        <v>22412</v>
       </c>
       <c r="C239" t="n">
-        <v>119.53</v>
+        <v>97.47</v>
       </c>
       <c r="D239" t="n">
-        <v>21607</v>
+        <v>15736</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>77</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="B240" t="n">
-        <v>24006</v>
+        <v>21622</v>
       </c>
       <c r="C240" t="n">
-        <v>75.88</v>
+        <v>81.77</v>
       </c>
       <c r="D240" t="n">
-        <v>23007</v>
+        <v>23185</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>12.96</v>
+        <v>91.86</v>
       </c>
       <c r="B241" t="n">
-        <v>24658</v>
+        <v>21810</v>
       </c>
       <c r="C241" t="n">
-        <v>13.26</v>
+        <v>99.59</v>
       </c>
       <c r="D241" t="n">
-        <v>13372</v>
+        <v>11831</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>96.79000000000001</v>
+        <v>92.12</v>
       </c>
       <c r="B242" t="n">
-        <v>36317</v>
+        <v>21917</v>
       </c>
       <c r="C242" t="n">
-        <v>96.75</v>
+        <v>97.75</v>
       </c>
       <c r="D242" t="n">
-        <v>13203</v>
+        <v>15918</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>106.41</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="B243" t="n">
-        <v>42801</v>
+        <v>22357</v>
       </c>
       <c r="C243" t="n">
-        <v>104.22</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="D243" t="n">
-        <v>22653</v>
+        <v>16134</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>98.69</v>
+        <v>92.69</v>
       </c>
       <c r="B244" t="n">
-        <v>44132</v>
+        <v>22563</v>
       </c>
       <c r="C244" t="n">
-        <v>95.44</v>
+        <v>93.64</v>
       </c>
       <c r="D244" t="n">
-        <v>24709</v>
+        <v>26468</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>100.83</v>
+        <v>92.8</v>
       </c>
       <c r="B245" t="n">
-        <v>44403</v>
+        <v>22249</v>
       </c>
       <c r="C245" t="n">
-        <v>100.63</v>
+        <v>90.95</v>
       </c>
       <c r="D245" t="n">
-        <v>10090</v>
+        <v>23804</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>98.18000000000001</v>
+        <v>93.37</v>
       </c>
       <c r="B246" t="n">
-        <v>40379</v>
+        <v>22226</v>
       </c>
       <c r="C246" t="n">
-        <v>94.36</v>
+        <v>80.92</v>
       </c>
       <c r="D246" t="n">
-        <v>18736</v>
+        <v>11338</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>106.94</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="B247" t="n">
-        <v>42091</v>
+        <v>23619</v>
       </c>
       <c r="C247" t="n">
-        <v>102.6</v>
+        <v>100.26</v>
       </c>
       <c r="D247" t="n">
-        <v>19069</v>
+        <v>28443</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>104.3</v>
+        <v>94.23</v>
       </c>
       <c r="B248" t="n">
-        <v>44454</v>
+        <v>23865</v>
       </c>
       <c r="C248" t="n">
-        <v>106.63</v>
+        <v>95.36</v>
       </c>
       <c r="D248" t="n">
-        <v>13322</v>
+        <v>14619</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>112.63</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="B249" t="n">
-        <v>23931</v>
+        <v>23580</v>
       </c>
       <c r="C249" t="n">
-        <v>110.25</v>
+        <v>78.78</v>
       </c>
       <c r="D249" t="n">
-        <v>24557</v>
+        <v>18945</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>97.73</v>
+        <v>94.27</v>
       </c>
       <c r="B250" t="n">
-        <v>39812</v>
+        <v>24175</v>
       </c>
       <c r="C250" t="n">
-        <v>95</v>
+        <v>95.92</v>
       </c>
       <c r="D250" t="n">
-        <v>25693</v>
+        <v>25260</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>108.14</v>
+        <v>94.45</v>
       </c>
       <c r="B251" t="n">
-        <v>37347</v>
+        <v>24740</v>
       </c>
       <c r="C251" t="n">
-        <v>110.59</v>
+        <v>78.75</v>
       </c>
       <c r="D251" t="n">
-        <v>19056</v>
+        <v>16567</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>111.89</v>
+        <v>94.92</v>
       </c>
       <c r="B252" t="n">
-        <v>28020</v>
+        <v>24940</v>
       </c>
       <c r="C252" t="n">
-        <v>111.86</v>
+        <v>83.47</v>
       </c>
       <c r="D252" t="n">
-        <v>23571</v>
+        <v>20007</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>112.81</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="B253" t="n">
-        <v>23726</v>
+        <v>25080</v>
       </c>
       <c r="C253" t="n">
-        <v>114.09</v>
+        <v>85.13</v>
       </c>
       <c r="D253" t="n">
-        <v>26355</v>
+        <v>28854</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>101.09</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="B254" t="n">
-        <v>45445</v>
+        <v>25061</v>
       </c>
       <c r="C254" t="n">
-        <v>100.25</v>
+        <v>106.35</v>
       </c>
       <c r="D254" t="n">
-        <v>29691</v>
+        <v>25449</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>90.56999999999999</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="B255" t="n">
-        <v>23382</v>
+        <v>25865</v>
       </c>
       <c r="C255" t="n">
-        <v>88.54000000000001</v>
+        <v>100.98</v>
       </c>
       <c r="D255" t="n">
-        <v>16916</v>
+        <v>26452</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>101.66</v>
+        <v>95.23</v>
       </c>
       <c r="B256" t="n">
-        <v>45513</v>
+        <v>26125</v>
       </c>
       <c r="C256" t="n">
-        <v>101.14</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="D256" t="n">
-        <v>12074</v>
+        <v>13720</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>100.26</v>
+        <v>96.06</v>
       </c>
       <c r="B257" t="n">
-        <v>45272</v>
+        <v>27351</v>
       </c>
       <c r="C257" t="n">
-        <v>99.89</v>
+        <v>89.87</v>
       </c>
       <c r="D257" t="n">
-        <v>23731</v>
+        <v>20898</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>99.52</v>
+        <v>96.92</v>
       </c>
       <c r="B258" t="n">
-        <v>42446</v>
+        <v>28390</v>
       </c>
       <c r="C258" t="n">
-        <v>101.63</v>
+        <v>84.89</v>
       </c>
       <c r="D258" t="n">
-        <v>16276</v>
+        <v>27023</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>111.66</v>
+        <v>98.45</v>
       </c>
       <c r="B259" t="n">
-        <v>26164</v>
+        <v>31302</v>
       </c>
       <c r="C259" t="n">
-        <v>108.9</v>
+        <v>111.81</v>
       </c>
       <c r="D259" t="n">
-        <v>24421</v>
+        <v>25061</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>157.2</v>
+        <v>98.66</v>
       </c>
       <c r="B260" t="n">
-        <v>25704</v>
+        <v>31161</v>
       </c>
       <c r="C260" t="n">
-        <v>155.68</v>
+        <v>106.58</v>
       </c>
       <c r="D260" t="n">
-        <v>11110</v>
+        <v>29386</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>95.26000000000001</v>
+        <v>98.66</v>
       </c>
       <c r="B261" t="n">
-        <v>33643</v>
+        <v>32997</v>
       </c>
       <c r="C261" t="n">
-        <v>93.53</v>
+        <v>107.11</v>
       </c>
       <c r="D261" t="n">
-        <v>12482</v>
+        <v>29868</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>111.48</v>
+        <v>99.08</v>
       </c>
       <c r="B262" t="n">
-        <v>28147</v>
+        <v>33157</v>
       </c>
       <c r="C262" t="n">
-        <v>109.44</v>
+        <v>102.05</v>
       </c>
       <c r="D262" t="n">
-        <v>16566</v>
+        <v>15040</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>109.78</v>
+        <v>99.12</v>
       </c>
       <c r="B263" t="n">
-        <v>29562</v>
+        <v>32823</v>
       </c>
       <c r="C263" t="n">
-        <v>112.54</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="D263" t="n">
-        <v>27606</v>
+        <v>29631</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>175</v>
+        <v>99.25</v>
       </c>
       <c r="B264" t="n">
-        <v>22533</v>
+        <v>33170</v>
       </c>
       <c r="C264" t="n">
-        <v>176.28</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D264" t="n">
-        <v>18600</v>
+        <v>27773</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>94.47</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="B265" t="n">
-        <v>34307</v>
+        <v>34605</v>
       </c>
       <c r="C265" t="n">
-        <v>94.81999999999999</v>
+        <v>111.44</v>
       </c>
       <c r="D265" t="n">
-        <v>19435</v>
+        <v>16834</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>173.36</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="B266" t="n">
-        <v>23321</v>
+        <v>35145</v>
       </c>
       <c r="C266" t="n">
-        <v>176.7</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="D266" t="n">
-        <v>14823</v>
+        <v>18167</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>104.44</v>
+        <v>100.5</v>
       </c>
       <c r="B267" t="n">
-        <v>47427</v>
+        <v>36284</v>
       </c>
       <c r="C267" t="n">
-        <v>101.13</v>
+        <v>102.63</v>
       </c>
       <c r="D267" t="n">
-        <v>15067</v>
+        <v>12113</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>102.48</v>
+        <v>100.52</v>
       </c>
       <c r="B268" t="n">
-        <v>45452</v>
+        <v>36375</v>
       </c>
       <c r="C268" t="n">
-        <v>101.86</v>
+        <v>92.34</v>
       </c>
       <c r="D268" t="n">
-        <v>19260</v>
+        <v>27716</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>101.69</v>
+        <v>101.07</v>
       </c>
       <c r="B269" t="n">
-        <v>46017</v>
+        <v>37139</v>
       </c>
       <c r="C269" t="n">
-        <v>105.31</v>
+        <v>97.36</v>
       </c>
       <c r="D269" t="n">
-        <v>21521</v>
+        <v>19088</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>111.22</v>
+        <v>101.28</v>
       </c>
       <c r="B270" t="n">
-        <v>29401</v>
+        <v>36793</v>
       </c>
       <c r="C270" t="n">
-        <v>115.34</v>
+        <v>94.7</v>
       </c>
       <c r="D270" t="n">
-        <v>29911</v>
+        <v>26099</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>92.86</v>
+        <v>101.34</v>
       </c>
       <c r="B271" t="n">
-        <v>28643</v>
+        <v>36794</v>
       </c>
       <c r="C271" t="n">
-        <v>93.86</v>
+        <v>113.37</v>
       </c>
       <c r="D271" t="n">
-        <v>25627</v>
+        <v>27961</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>94.2</v>
+        <v>102.5</v>
       </c>
       <c r="B272" t="n">
-        <v>32714</v>
+        <v>38455</v>
       </c>
       <c r="C272" t="n">
-        <v>93.33</v>
+        <v>100.35</v>
       </c>
       <c r="D272" t="n">
-        <v>26843</v>
+        <v>12061</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>109.15</v>
+        <v>102.52</v>
       </c>
       <c r="B273" t="n">
-        <v>33998</v>
+        <v>37117</v>
       </c>
       <c r="C273" t="n">
-        <v>112.67</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="D273" t="n">
-        <v>18744</v>
+        <v>14697</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>113.16</v>
+        <v>103.35</v>
       </c>
       <c r="B274" t="n">
-        <v>23351</v>
+        <v>37088</v>
       </c>
       <c r="C274" t="n">
-        <v>109.64</v>
+        <v>106.87</v>
       </c>
       <c r="D274" t="n">
-        <v>14629</v>
+        <v>29398</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>111.8</v>
+        <v>103.4</v>
       </c>
       <c r="B275" t="n">
-        <v>27405</v>
+        <v>36328</v>
       </c>
       <c r="C275" t="n">
-        <v>115.93</v>
+        <v>133.44</v>
       </c>
       <c r="D275" t="n">
-        <v>15282</v>
+        <v>24565</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>94.58</v>
+        <v>103.42</v>
       </c>
       <c r="B276" t="n">
-        <v>32344</v>
+        <v>37592</v>
       </c>
       <c r="C276" t="n">
-        <v>94.77</v>
+        <v>105.51</v>
       </c>
       <c r="D276" t="n">
-        <v>18188</v>
+        <v>27108</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>99.34999999999999</v>
+        <v>103.83</v>
       </c>
       <c r="B277" t="n">
-        <v>45439</v>
+        <v>38498</v>
       </c>
       <c r="C277" t="n">
-        <v>101.31</v>
+        <v>91.42</v>
       </c>
       <c r="D277" t="n">
-        <v>29784</v>
+        <v>24953</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>94.06</v>
+        <v>104.29</v>
       </c>
       <c r="B278" t="n">
-        <v>29127</v>
+        <v>38552</v>
       </c>
       <c r="C278" t="n">
-        <v>90.54000000000001</v>
+        <v>115.98</v>
       </c>
       <c r="D278" t="n">
-        <v>18585</v>
+        <v>24321</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>93.37</v>
+        <v>104.76</v>
       </c>
       <c r="B279" t="n">
-        <v>31710</v>
+        <v>36477</v>
       </c>
       <c r="C279" t="n">
-        <v>95.44</v>
+        <v>89.02</v>
       </c>
       <c r="D279" t="n">
-        <v>17161</v>
+        <v>24123</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>94.76000000000001</v>
+        <v>105.69</v>
       </c>
       <c r="B280" t="n">
-        <v>32450</v>
+        <v>36027</v>
       </c>
       <c r="C280" t="n">
-        <v>94.7</v>
+        <v>89.25</v>
       </c>
       <c r="D280" t="n">
-        <v>15072</v>
+        <v>27434</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>110.14</v>
+        <v>105.76</v>
       </c>
       <c r="B281" t="n">
-        <v>29508</v>
+        <v>34247</v>
       </c>
       <c r="C281" t="n">
-        <v>114.76</v>
+        <v>102.9</v>
       </c>
       <c r="D281" t="n">
-        <v>29974</v>
+        <v>10213</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>107.42</v>
+        <v>105.83</v>
       </c>
       <c r="B282" t="n">
-        <v>40285</v>
+        <v>35579</v>
       </c>
       <c r="C282" t="n">
-        <v>106.63</v>
+        <v>112.93</v>
       </c>
       <c r="D282" t="n">
-        <v>11703</v>
+        <v>25484</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>104.98</v>
+        <v>106.28</v>
       </c>
       <c r="B283" t="n">
-        <v>46243</v>
+        <v>34603</v>
       </c>
       <c r="C283" t="n">
-        <v>102.04</v>
+        <v>102.03</v>
       </c>
       <c r="D283" t="n">
-        <v>25436</v>
+        <v>19949</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>150.85</v>
+        <v>106.47</v>
       </c>
       <c r="B284" t="n">
-        <v>22823</v>
+        <v>35850</v>
       </c>
       <c r="C284" t="n">
-        <v>146.77</v>
+        <v>123.32</v>
       </c>
       <c r="D284" t="n">
-        <v>21405</v>
+        <v>22301</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>110.65</v>
+        <v>106.51</v>
       </c>
       <c r="B285" t="n">
-        <v>31434</v>
+        <v>34244</v>
       </c>
       <c r="C285" t="n">
-        <v>112.06</v>
+        <v>114.05</v>
       </c>
       <c r="D285" t="n">
-        <v>26378</v>
+        <v>24814</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>106.78</v>
+        <v>106.71</v>
       </c>
       <c r="B286" t="n">
-        <v>41159</v>
+        <v>34164</v>
       </c>
       <c r="C286" t="n">
-        <v>109.74</v>
+        <v>121.12</v>
       </c>
       <c r="D286" t="n">
-        <v>22215</v>
+        <v>12203</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>28.09</v>
+        <v>106.83</v>
       </c>
       <c r="B287" t="n">
-        <v>22124</v>
+        <v>33821</v>
       </c>
       <c r="C287" t="n">
-        <v>27.11</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="D287" t="n">
-        <v>16679</v>
+        <v>26736</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>103.99</v>
+        <v>107.17</v>
       </c>
       <c r="B288" t="n">
-        <v>46251</v>
+        <v>33207</v>
       </c>
       <c r="C288" t="n">
-        <v>105.89</v>
+        <v>110.36</v>
       </c>
       <c r="D288" t="n">
-        <v>26330</v>
+        <v>13296</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>114.2</v>
+        <v>108.29</v>
       </c>
       <c r="B289" t="n">
-        <v>22616</v>
+        <v>31324</v>
       </c>
       <c r="C289" t="n">
-        <v>117.47</v>
+        <v>94.19</v>
       </c>
       <c r="D289" t="n">
-        <v>17165</v>
+        <v>16455</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1.35</v>
+        <v>108.81</v>
       </c>
       <c r="B290" t="n">
-        <v>25095</v>
+        <v>29071</v>
       </c>
       <c r="C290" t="n">
-        <v>1.29</v>
+        <v>95.27</v>
       </c>
       <c r="D290" t="n">
-        <v>22606</v>
+        <v>23979</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>99.38</v>
+        <v>108.84</v>
       </c>
       <c r="B291" t="n">
-        <v>41900</v>
+        <v>28752</v>
       </c>
       <c r="C291" t="n">
-        <v>99.22</v>
+        <v>111.88</v>
       </c>
       <c r="D291" t="n">
-        <v>23181</v>
+        <v>22078</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>104.73</v>
+        <v>109.08</v>
       </c>
       <c r="B292" t="n">
-        <v>47875</v>
+        <v>28302</v>
       </c>
       <c r="C292" t="n">
-        <v>106.38</v>
+        <v>103.87</v>
       </c>
       <c r="D292" t="n">
-        <v>28328</v>
+        <v>13999</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>79.44</v>
+        <v>109.11</v>
       </c>
       <c r="B293" t="n">
-        <v>27689</v>
+        <v>28979</v>
       </c>
       <c r="C293" t="n">
-        <v>78.84</v>
+        <v>84.42</v>
       </c>
       <c r="D293" t="n">
-        <v>11515</v>
+        <v>10040</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>98.52</v>
+        <v>109.19</v>
       </c>
       <c r="B294" t="n">
-        <v>42177</v>
+        <v>28293</v>
       </c>
       <c r="C294" t="n">
-        <v>98.13</v>
+        <v>102.93</v>
       </c>
       <c r="D294" t="n">
-        <v>29706</v>
+        <v>22015</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>108.04</v>
+        <v>109.21</v>
       </c>
       <c r="B295" t="n">
-        <v>39482</v>
+        <v>28289</v>
       </c>
       <c r="C295" t="n">
-        <v>106.95</v>
+        <v>122.14</v>
       </c>
       <c r="D295" t="n">
-        <v>13739</v>
+        <v>24841</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>114.46</v>
+        <v>109.31</v>
       </c>
       <c r="B296" t="n">
-        <v>25961</v>
+        <v>27466</v>
       </c>
       <c r="C296" t="n">
-        <v>110.24</v>
+        <v>109.61</v>
       </c>
       <c r="D296" t="n">
-        <v>24566</v>
+        <v>27280</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>99.5</v>
+        <v>109.35</v>
       </c>
       <c r="B297" t="n">
-        <v>43285</v>
+        <v>27782</v>
       </c>
       <c r="C297" t="n">
-        <v>101.06</v>
+        <v>128.3</v>
       </c>
       <c r="D297" t="n">
-        <v>17224</v>
+        <v>20663</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>95.09999999999999</v>
+        <v>109.69</v>
       </c>
       <c r="B298" t="n">
-        <v>35588</v>
+        <v>27108</v>
       </c>
       <c r="C298" t="n">
-        <v>93.64</v>
+        <v>120.75</v>
       </c>
       <c r="D298" t="n">
-        <v>14404</v>
+        <v>16791</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>102.25</v>
+        <v>109.79</v>
       </c>
       <c r="B299" t="n">
-        <v>47517</v>
+        <v>28351</v>
       </c>
       <c r="C299" t="n">
-        <v>103.49</v>
+        <v>102.61</v>
       </c>
       <c r="D299" t="n">
-        <v>26443</v>
+        <v>16401</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>94.45999999999999</v>
+        <v>110.29</v>
       </c>
       <c r="B300" t="n">
-        <v>31747</v>
+        <v>26224</v>
       </c>
       <c r="C300" t="n">
-        <v>96.88</v>
+        <v>105.68</v>
       </c>
       <c r="D300" t="n">
-        <v>13910</v>
+        <v>18858</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>102.29</v>
+        <v>110.31</v>
       </c>
       <c r="B301" t="n">
-        <v>45729</v>
+        <v>25813</v>
       </c>
       <c r="C301" t="n">
-        <v>106.05</v>
+        <v>100.93</v>
       </c>
       <c r="D301" t="n">
-        <v>23289</v>
+        <v>15764</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>93.84999999999999</v>
+        <v>110.71</v>
       </c>
       <c r="B302" t="n">
-        <v>30047</v>
+        <v>25254</v>
       </c>
       <c r="C302" t="n">
-        <v>91.42</v>
+        <v>104.29</v>
       </c>
       <c r="D302" t="n">
-        <v>19022</v>
+        <v>20560</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>155.41</v>
+        <v>111.12</v>
       </c>
       <c r="B303" t="n">
-        <v>23138</v>
+        <v>25672</v>
       </c>
       <c r="C303" t="n">
-        <v>161.22</v>
+        <v>88.37</v>
       </c>
       <c r="D303" t="n">
-        <v>16482</v>
+        <v>13307</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>51.52</v>
+        <v>111.15</v>
       </c>
       <c r="B304" t="n">
-        <v>25419</v>
+        <v>25193</v>
       </c>
       <c r="C304" t="n">
-        <v>50.6</v>
+        <v>130.22</v>
       </c>
       <c r="D304" t="n">
-        <v>16919</v>
+        <v>28081</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>109.56</v>
+        <v>111.65</v>
       </c>
       <c r="B305" t="n">
-        <v>34057</v>
+        <v>22843</v>
       </c>
       <c r="C305" t="n">
-        <v>106.07</v>
+        <v>120.87</v>
       </c>
       <c r="D305" t="n">
-        <v>23973</v>
+        <v>29117</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>98.17</v>
+        <v>111.82</v>
       </c>
       <c r="B306" t="n">
-        <v>38281</v>
+        <v>24783</v>
       </c>
       <c r="C306" t="n">
-        <v>97.63</v>
+        <v>101.06</v>
       </c>
       <c r="D306" t="n">
-        <v>15523</v>
+        <v>24533</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>95.79000000000001</v>
+        <v>111.97</v>
       </c>
       <c r="B307" t="n">
-        <v>34245</v>
+        <v>23277</v>
       </c>
       <c r="C307" t="n">
-        <v>98.84999999999999</v>
+        <v>122.01</v>
       </c>
       <c r="D307" t="n">
-        <v>29915</v>
+        <v>23066</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>130.66</v>
+        <v>111.99</v>
       </c>
       <c r="B308" t="n">
-        <v>25012</v>
+        <v>24000</v>
       </c>
       <c r="C308" t="n">
-        <v>130.52</v>
+        <v>102.73</v>
       </c>
       <c r="D308" t="n">
-        <v>20305</v>
+        <v>22136</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>111.36</v>
+        <v>112.06</v>
       </c>
       <c r="B309" t="n">
-        <v>31711</v>
+        <v>22760</v>
       </c>
       <c r="C309" t="n">
-        <v>110.61</v>
+        <v>132.45</v>
       </c>
       <c r="D309" t="n">
-        <v>27185</v>
+        <v>21475</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>105.83</v>
+        <v>112.12</v>
       </c>
       <c r="B310" t="n">
-        <v>44618</v>
+        <v>24301</v>
       </c>
       <c r="C310" t="n">
-        <v>108.27</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="D310" t="n">
-        <v>12188</v>
+        <v>11148</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>12.43</v>
+        <v>112.29</v>
       </c>
       <c r="B311" t="n">
-        <v>23884</v>
+        <v>22563</v>
       </c>
       <c r="C311" t="n">
-        <v>13.49</v>
+        <v>92.02</v>
       </c>
       <c r="D311" t="n">
-        <v>18038</v>
+        <v>29552</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>91.95</v>
+        <v>112.46</v>
       </c>
       <c r="B312" t="n">
-        <v>28135</v>
+        <v>21514</v>
       </c>
       <c r="C312" t="n">
-        <v>90.8</v>
+        <v>127.88</v>
       </c>
       <c r="D312" t="n">
-        <v>25579</v>
+        <v>16346</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>79.13</v>
+        <v>112.74</v>
       </c>
       <c r="B313" t="n">
-        <v>22902</v>
+        <v>23681</v>
       </c>
       <c r="C313" t="n">
-        <v>76.44</v>
+        <v>128.8</v>
       </c>
       <c r="D313" t="n">
-        <v>29037</v>
+        <v>25899</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>103.81</v>
+        <v>113.02</v>
       </c>
       <c r="B314" t="n">
-        <v>48309</v>
+        <v>23733</v>
       </c>
       <c r="C314" t="n">
-        <v>103.27</v>
+        <v>95.95</v>
       </c>
       <c r="D314" t="n">
-        <v>13017</v>
+        <v>23606</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>114.32</v>
+        <v>113.71</v>
       </c>
       <c r="B315" t="n">
-        <v>23523</v>
+        <v>20485</v>
       </c>
       <c r="C315" t="n">
-        <v>114.85</v>
+        <v>100.59</v>
       </c>
       <c r="D315" t="n">
-        <v>27811</v>
+        <v>28875</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>110.03</v>
+        <v>114.15</v>
       </c>
       <c r="B316" t="n">
-        <v>32516</v>
+        <v>22055</v>
       </c>
       <c r="C316" t="n">
-        <v>111.81</v>
+        <v>136.52</v>
       </c>
       <c r="D316" t="n">
-        <v>19735</v>
+        <v>20921</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>97.37</v>
+        <v>114.24</v>
       </c>
       <c r="B317" t="n">
-        <v>38337</v>
+        <v>20332</v>
       </c>
       <c r="C317" t="n">
-        <v>93.29000000000001</v>
+        <v>117.32</v>
       </c>
       <c r="D317" t="n">
-        <v>29408</v>
+        <v>29955</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>112.76</v>
+        <v>114.44</v>
       </c>
       <c r="B318" t="n">
-        <v>27315</v>
+        <v>20809</v>
       </c>
       <c r="C318" t="n">
-        <v>111.82</v>
+        <v>87.17</v>
       </c>
       <c r="D318" t="n">
-        <v>18664</v>
+        <v>29582</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>110.7</v>
+        <v>114.5</v>
       </c>
       <c r="B319" t="n">
-        <v>29746</v>
+        <v>20485</v>
       </c>
       <c r="C319" t="n">
-        <v>107</v>
+        <v>140.99</v>
       </c>
       <c r="D319" t="n">
-        <v>16526</v>
+        <v>27927</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>78.31</v>
+        <v>114.53</v>
       </c>
       <c r="B320" t="n">
-        <v>25466</v>
+        <v>20725</v>
       </c>
       <c r="C320" t="n">
-        <v>80.48</v>
+        <v>112.62</v>
       </c>
       <c r="D320" t="n">
-        <v>14875</v>
+        <v>18832</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>104.4</v>
+        <v>114.69</v>
       </c>
       <c r="B321" t="n">
-        <v>43887</v>
+        <v>21433</v>
       </c>
       <c r="C321" t="n">
-        <v>101.73</v>
+        <v>112.97</v>
       </c>
       <c r="D321" t="n">
-        <v>17479</v>
+        <v>27915</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>92.59</v>
+        <v>114.7</v>
       </c>
       <c r="B322" t="n">
-        <v>25337</v>
+        <v>20960</v>
       </c>
       <c r="C322" t="n">
-        <v>91.56</v>
+        <v>129.74</v>
       </c>
       <c r="D322" t="n">
-        <v>15757</v>
+        <v>24983</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>98.02</v>
+        <v>114.82</v>
       </c>
       <c r="B323" t="n">
-        <v>40722</v>
+        <v>20573</v>
       </c>
       <c r="C323" t="n">
-        <v>94.33</v>
+        <v>102.58</v>
       </c>
       <c r="D323" t="n">
-        <v>21351</v>
+        <v>28406</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>133.53</v>
+        <v>115.5</v>
       </c>
       <c r="B324" t="n">
-        <v>23005</v>
+        <v>21845</v>
       </c>
       <c r="C324" t="n">
-        <v>138.01</v>
+        <v>106.59</v>
       </c>
       <c r="D324" t="n">
-        <v>28403</v>
+        <v>15963</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>92.65000000000001</v>
+        <v>115.75</v>
       </c>
       <c r="B325" t="n">
-        <v>23471</v>
+        <v>19638</v>
       </c>
       <c r="C325" t="n">
-        <v>93.09999999999999</v>
+        <v>104.55</v>
       </c>
       <c r="D325" t="n">
-        <v>11536</v>
+        <v>15654</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>127.7</v>
+        <v>115.79</v>
       </c>
       <c r="B326" t="n">
-        <v>22503</v>
+        <v>19715</v>
       </c>
       <c r="C326" t="n">
-        <v>128.05</v>
+        <v>105.74</v>
       </c>
       <c r="D326" t="n">
-        <v>28825</v>
+        <v>26224</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>95.68000000000001</v>
+        <v>117.05</v>
       </c>
       <c r="B327" t="n">
-        <v>33980</v>
+        <v>21615</v>
       </c>
       <c r="C327" t="n">
-        <v>96.69</v>
+        <v>107.82</v>
       </c>
       <c r="D327" t="n">
-        <v>20266</v>
+        <v>16614</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>113</v>
+        <v>117.14</v>
       </c>
       <c r="B328" t="n">
-        <v>23820</v>
+        <v>18381</v>
       </c>
       <c r="C328" t="n">
-        <v>109.17</v>
+        <v>116.51</v>
       </c>
       <c r="D328" t="n">
-        <v>29326</v>
+        <v>26264</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>110.68</v>
+        <v>119.51</v>
       </c>
       <c r="B329" t="n">
-        <v>28900</v>
+        <v>19262</v>
       </c>
       <c r="C329" t="n">
-        <v>106.31</v>
+        <v>95.67</v>
       </c>
       <c r="D329" t="n">
-        <v>25706</v>
+        <v>21332</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>99.19</v>
+        <v>119.99</v>
       </c>
       <c r="B330" t="n">
-        <v>43136</v>
+        <v>21138</v>
       </c>
       <c r="C330" t="n">
-        <v>101.43</v>
+        <v>113.08</v>
       </c>
       <c r="D330" t="n">
-        <v>18055</v>
+        <v>26586</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>139.65</v>
+        <v>120.41</v>
       </c>
       <c r="B331" t="n">
-        <v>22587</v>
+        <v>20050</v>
       </c>
       <c r="C331" t="n">
-        <v>138.55</v>
+        <v>137.7</v>
       </c>
       <c r="D331" t="n">
-        <v>23397</v>
+        <v>15097</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>99.89</v>
+        <v>120.84</v>
       </c>
       <c r="B332" t="n">
-        <v>43484</v>
+        <v>19255</v>
       </c>
       <c r="C332" t="n">
-        <v>98.08</v>
+        <v>121.43</v>
       </c>
       <c r="D332" t="n">
-        <v>21570</v>
+        <v>13868</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>104.96</v>
+        <v>120.88</v>
       </c>
       <c r="B333" t="n">
-        <v>46528</v>
+        <v>18768</v>
       </c>
       <c r="C333" t="n">
-        <v>104.34</v>
+        <v>107.19</v>
       </c>
       <c r="D333" t="n">
-        <v>26346</v>
+        <v>11002</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>127.46</v>
+        <v>121.22</v>
       </c>
       <c r="B334" t="n">
-        <v>20371</v>
+        <v>18558</v>
       </c>
       <c r="C334" t="n">
-        <v>131.91</v>
+        <v>144.8</v>
       </c>
       <c r="D334" t="n">
-        <v>17661</v>
+        <v>16958</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>106.09</v>
+        <v>121.33</v>
       </c>
       <c r="B335" t="n">
-        <v>45890</v>
+        <v>18007</v>
       </c>
       <c r="C335" t="n">
-        <v>110.02</v>
+        <v>130.09</v>
       </c>
       <c r="D335" t="n">
-        <v>22110</v>
+        <v>20230</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>95.79000000000001</v>
+        <v>121.68</v>
       </c>
       <c r="B336" t="n">
-        <v>34686</v>
+        <v>16789</v>
       </c>
       <c r="C336" t="n">
-        <v>97.63</v>
+        <v>141.7</v>
       </c>
       <c r="D336" t="n">
-        <v>27747</v>
+        <v>24212</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>110.13</v>
+        <v>121.69</v>
       </c>
       <c r="B337" t="n">
-        <v>30469</v>
+        <v>21372</v>
       </c>
       <c r="C337" t="n">
-        <v>107.58</v>
+        <v>113.79</v>
       </c>
       <c r="D337" t="n">
-        <v>17084</v>
+        <v>20303</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>114.35</v>
+        <v>122.27</v>
       </c>
       <c r="B338" t="n">
-        <v>24036</v>
+        <v>20548</v>
       </c>
       <c r="C338" t="n">
-        <v>112.89</v>
+        <v>112.03</v>
       </c>
       <c r="D338" t="n">
-        <v>29189</v>
+        <v>15627</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>114.71</v>
+        <v>122.27</v>
       </c>
       <c r="B339" t="n">
-        <v>21973</v>
+        <v>18699</v>
       </c>
       <c r="C339" t="n">
-        <v>112.12</v>
+        <v>98.22</v>
       </c>
       <c r="D339" t="n">
-        <v>18703</v>
+        <v>25935</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>105.92</v>
+        <v>122.28</v>
       </c>
       <c r="B340" t="n">
-        <v>47269</v>
+        <v>20943</v>
       </c>
       <c r="C340" t="n">
-        <v>108.51</v>
+        <v>126.21</v>
       </c>
       <c r="D340" t="n">
-        <v>19966</v>
+        <v>21555</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>134.08</v>
+        <v>122.33</v>
       </c>
       <c r="B341" t="n">
-        <v>23541</v>
+        <v>20471</v>
       </c>
       <c r="C341" t="n">
-        <v>133</v>
+        <v>142.07</v>
       </c>
       <c r="D341" t="n">
-        <v>20070</v>
+        <v>15449</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>99.95999999999999</v>
+        <v>122.34</v>
       </c>
       <c r="B342" t="n">
-        <v>42955</v>
+        <v>19942</v>
       </c>
       <c r="C342" t="n">
-        <v>96.33</v>
+        <v>154.6</v>
       </c>
       <c r="D342" t="n">
-        <v>17221</v>
+        <v>29480</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>5.41</v>
+        <v>122.72</v>
       </c>
       <c r="B343" t="n">
-        <v>23541</v>
+        <v>19134</v>
       </c>
       <c r="C343" t="n">
-        <v>5.73</v>
+        <v>118.03</v>
       </c>
       <c r="D343" t="n">
-        <v>23968</v>
+        <v>20299</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>103.53</v>
+        <v>122.72</v>
       </c>
       <c r="B344" t="n">
-        <v>48247</v>
+        <v>20147</v>
       </c>
       <c r="C344" t="n">
-        <v>102.36</v>
+        <v>119.27</v>
       </c>
       <c r="D344" t="n">
-        <v>24391</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>93.91</v>
+        <v>123.39</v>
       </c>
       <c r="B345" t="n">
-        <v>30231</v>
+        <v>17953</v>
       </c>
       <c r="C345" t="n">
-        <v>90.92</v>
+        <v>124.59</v>
       </c>
       <c r="D345" t="n">
-        <v>24387</v>
+        <v>13448</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>114.45</v>
+        <v>123.79</v>
       </c>
       <c r="B346" t="n">
-        <v>24391</v>
+        <v>18035</v>
       </c>
       <c r="C346" t="n">
-        <v>113.25</v>
+        <v>139.88</v>
       </c>
       <c r="D346" t="n">
-        <v>10676</v>
+        <v>14523</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>98.45999999999999</v>
+        <v>124.36</v>
       </c>
       <c r="B347" t="n">
-        <v>40998</v>
+        <v>18799</v>
       </c>
       <c r="C347" t="n">
-        <v>95.15000000000001</v>
+        <v>115.3</v>
       </c>
       <c r="D347" t="n">
-        <v>11486</v>
+        <v>18786</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>105.49</v>
+        <v>125.03</v>
       </c>
       <c r="B348" t="n">
-        <v>46526</v>
+        <v>18541</v>
       </c>
       <c r="C348" t="n">
-        <v>107.23</v>
+        <v>142.87</v>
       </c>
       <c r="D348" t="n">
-        <v>21503</v>
+        <v>22414</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>97.56999999999999</v>
+        <v>125.41</v>
       </c>
       <c r="B349" t="n">
-        <v>39472</v>
+        <v>20311</v>
       </c>
       <c r="C349" t="n">
-        <v>99.90000000000001</v>
+        <v>115.29</v>
       </c>
       <c r="D349" t="n">
-        <v>25667</v>
+        <v>12184</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>109.5</v>
+        <v>125.53</v>
       </c>
       <c r="B350" t="n">
-        <v>34227</v>
+        <v>20448</v>
       </c>
       <c r="C350" t="n">
-        <v>106.65</v>
+        <v>130.98</v>
       </c>
       <c r="D350" t="n">
-        <v>24533</v>
+        <v>24690</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>108.47</v>
+        <v>125.84</v>
       </c>
       <c r="B351" t="n">
-        <v>38457</v>
+        <v>20325</v>
       </c>
       <c r="C351" t="n">
-        <v>106.32</v>
+        <v>118.22</v>
       </c>
       <c r="D351" t="n">
-        <v>29731</v>
+        <v>12806</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>101.88</v>
+        <v>125.99</v>
       </c>
       <c r="B352" t="n">
-        <v>45957</v>
+        <v>21663</v>
       </c>
       <c r="C352" t="n">
-        <v>100.76</v>
+        <v>139.34</v>
       </c>
       <c r="D352" t="n">
-        <v>10848</v>
+        <v>13245</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>113.68</v>
+        <v>126.04</v>
       </c>
       <c r="B353" t="n">
-        <v>26273</v>
+        <v>18550</v>
       </c>
       <c r="C353" t="n">
-        <v>112.35</v>
+        <v>111.77</v>
       </c>
       <c r="D353" t="n">
-        <v>26639</v>
+        <v>18829</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>77.67</v>
+        <v>126.07</v>
       </c>
       <c r="B354" t="n">
-        <v>23149</v>
+        <v>19568</v>
       </c>
       <c r="C354" t="n">
-        <v>79.84999999999999</v>
+        <v>105.57</v>
       </c>
       <c r="D354" t="n">
-        <v>12840</v>
+        <v>21277</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>88</v>
+        <v>126.29</v>
       </c>
       <c r="B355" t="n">
-        <v>24279</v>
+        <v>18989</v>
       </c>
       <c r="C355" t="n">
-        <v>88.13</v>
+        <v>107.39</v>
       </c>
       <c r="D355" t="n">
-        <v>28235</v>
+        <v>18144</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>110.22</v>
+        <v>128.1</v>
       </c>
       <c r="B356" t="n">
-        <v>30325</v>
+        <v>21234</v>
       </c>
       <c r="C356" t="n">
-        <v>113.32</v>
+        <v>110.55</v>
       </c>
       <c r="D356" t="n">
-        <v>17848</v>
+        <v>26706</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>156.33</v>
+        <v>128.11</v>
       </c>
       <c r="B357" t="n">
-        <v>21916</v>
+        <v>18743</v>
       </c>
       <c r="C357" t="n">
-        <v>155.66</v>
+        <v>147.89</v>
       </c>
       <c r="D357" t="n">
-        <v>16502</v>
+        <v>15627</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>92.09999999999999</v>
+        <v>128.26</v>
       </c>
       <c r="B358" t="n">
-        <v>25417</v>
+        <v>20117</v>
       </c>
       <c r="C358" t="n">
-        <v>93.73</v>
+        <v>131.42</v>
       </c>
       <c r="D358" t="n">
-        <v>15734</v>
+        <v>16882</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>106.49</v>
+        <v>128.36</v>
       </c>
       <c r="B359" t="n">
-        <v>42742</v>
+        <v>17596</v>
       </c>
       <c r="C359" t="n">
-        <v>110.71</v>
+        <v>131.38</v>
       </c>
       <c r="D359" t="n">
-        <v>29144</v>
+        <v>26279</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>113.06</v>
+        <v>128.83</v>
       </c>
       <c r="B360" t="n">
-        <v>26021</v>
+        <v>20493</v>
       </c>
       <c r="C360" t="n">
-        <v>113.27</v>
+        <v>123.93</v>
       </c>
       <c r="D360" t="n">
-        <v>13287</v>
+        <v>29847</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>126.49</v>
+        <v>129.37</v>
       </c>
       <c r="B361" t="n">
-        <v>24406</v>
+        <v>18162</v>
       </c>
       <c r="C361" t="n">
-        <v>121.96</v>
+        <v>144.12</v>
       </c>
       <c r="D361" t="n">
-        <v>24623</v>
+        <v>22064</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>106.07</v>
+        <v>129.66</v>
       </c>
       <c r="B362" t="n">
-        <v>45069</v>
+        <v>19194</v>
       </c>
       <c r="C362" t="n">
-        <v>107.15</v>
+        <v>113.77</v>
       </c>
       <c r="D362" t="n">
-        <v>22048</v>
+        <v>20869</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>110.52</v>
+        <v>130.29</v>
       </c>
       <c r="B363" t="n">
-        <v>30516</v>
+        <v>21747</v>
       </c>
       <c r="C363" t="n">
-        <v>111.1</v>
+        <v>112.33</v>
       </c>
       <c r="D363" t="n">
-        <v>19626</v>
+        <v>29850</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>99.37</v>
+        <v>131</v>
       </c>
       <c r="B364" t="n">
-        <v>42654</v>
+        <v>19910</v>
       </c>
       <c r="C364" t="n">
-        <v>97.87</v>
+        <v>117.43</v>
       </c>
       <c r="D364" t="n">
-        <v>22466</v>
+        <v>15975</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>89.23999999999999</v>
+        <v>131.76</v>
       </c>
       <c r="B365" t="n">
-        <v>26756</v>
+        <v>20375</v>
       </c>
       <c r="C365" t="n">
-        <v>86.98</v>
+        <v>148.57</v>
       </c>
       <c r="D365" t="n">
-        <v>22913</v>
+        <v>26631</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>90.38</v>
+        <v>132.08</v>
       </c>
       <c r="B366" t="n">
-        <v>21382</v>
+        <v>18368</v>
       </c>
       <c r="C366" t="n">
-        <v>88.48</v>
+        <v>137.27</v>
       </c>
       <c r="D366" t="n">
-        <v>27485</v>
+        <v>14688</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>102.95</v>
+        <v>132.21</v>
       </c>
       <c r="B367" t="n">
-        <v>47094</v>
+        <v>18706</v>
       </c>
       <c r="C367" t="n">
-        <v>103.2</v>
+        <v>122.91</v>
       </c>
       <c r="D367" t="n">
-        <v>22489</v>
+        <v>17308</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>103.02</v>
+        <v>132.44</v>
       </c>
       <c r="B368" t="n">
-        <v>48997</v>
+        <v>20501</v>
       </c>
       <c r="C368" t="n">
-        <v>100.34</v>
+        <v>133.71</v>
       </c>
       <c r="D368" t="n">
-        <v>11732</v>
+        <v>27005</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>99.38</v>
+        <v>132.56</v>
       </c>
       <c r="B369" t="n">
-        <v>40750</v>
+        <v>19620</v>
       </c>
       <c r="C369" t="n">
-        <v>102.7</v>
+        <v>140.36</v>
       </c>
       <c r="D369" t="n">
-        <v>29410</v>
+        <v>13081</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>22.88</v>
+        <v>132.58</v>
       </c>
       <c r="B370" t="n">
-        <v>23532</v>
+        <v>21821</v>
       </c>
       <c r="C370" t="n">
-        <v>23.19</v>
+        <v>127.78</v>
       </c>
       <c r="D370" t="n">
-        <v>21369</v>
+        <v>13267</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>109.3</v>
+        <v>132.86</v>
       </c>
       <c r="B371" t="n">
-        <v>35161</v>
+        <v>19724</v>
       </c>
       <c r="C371" t="n">
-        <v>112.52</v>
+        <v>121.89</v>
       </c>
       <c r="D371" t="n">
-        <v>27537</v>
+        <v>26617</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>114.08</v>
+        <v>132.91</v>
       </c>
       <c r="B372" t="n">
-        <v>22233</v>
+        <v>19493</v>
       </c>
       <c r="C372" t="n">
-        <v>117.67</v>
+        <v>124.86</v>
       </c>
       <c r="D372" t="n">
-        <v>12565</v>
+        <v>20672</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>95.98</v>
+        <v>134.09</v>
       </c>
       <c r="B373" t="n">
-        <v>37532</v>
+        <v>18045</v>
       </c>
       <c r="C373" t="n">
-        <v>92.53</v>
+        <v>142.53</v>
       </c>
       <c r="D373" t="n">
-        <v>27255</v>
+        <v>23359</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>91.73</v>
+        <v>134.11</v>
       </c>
       <c r="B374" t="n">
-        <v>24392</v>
+        <v>21696</v>
       </c>
       <c r="C374" t="n">
-        <v>94.81999999999999</v>
+        <v>139.1</v>
       </c>
       <c r="D374" t="n">
-        <v>18319</v>
+        <v>25490</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>155.11</v>
+        <v>134.19</v>
       </c>
       <c r="B375" t="n">
-        <v>23856</v>
+        <v>19108</v>
       </c>
       <c r="C375" t="n">
-        <v>155.03</v>
+        <v>132.09</v>
       </c>
       <c r="D375" t="n">
-        <v>29165</v>
+        <v>18432</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>22</v>
+        <v>134.27</v>
       </c>
       <c r="B376" t="n">
-        <v>21246</v>
+        <v>19699</v>
       </c>
       <c r="C376" t="n">
-        <v>22.41</v>
+        <v>144.44</v>
       </c>
       <c r="D376" t="n">
-        <v>10617</v>
+        <v>18406</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>19.95</v>
+        <v>134.4</v>
       </c>
       <c r="B377" t="n">
-        <v>20656</v>
+        <v>19186</v>
       </c>
       <c r="C377" t="n">
-        <v>19.33</v>
+        <v>148.94</v>
       </c>
       <c r="D377" t="n">
-        <v>25962</v>
+        <v>27104</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>113.66</v>
+        <v>134.46</v>
       </c>
       <c r="B378" t="n">
-        <v>22441</v>
+        <v>23488</v>
       </c>
       <c r="C378" t="n">
-        <v>109.29</v>
+        <v>119.8</v>
       </c>
       <c r="D378" t="n">
-        <v>26413</v>
+        <v>16369</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>109.25</v>
+        <v>134.62</v>
       </c>
       <c r="B379" t="n">
-        <v>35101</v>
+        <v>20543</v>
       </c>
       <c r="C379" t="n">
-        <v>105.33</v>
+        <v>155.95</v>
       </c>
       <c r="D379" t="n">
-        <v>16554</v>
+        <v>18602</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>99.83</v>
+        <v>135.28</v>
       </c>
       <c r="B380" t="n">
-        <v>43661</v>
+        <v>18800</v>
       </c>
       <c r="C380" t="n">
-        <v>97.76000000000001</v>
+        <v>146.63</v>
       </c>
       <c r="D380" t="n">
-        <v>11486</v>
+        <v>28411</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>92.34</v>
+        <v>135.29</v>
       </c>
       <c r="B381" t="n">
-        <v>26283</v>
+        <v>21311</v>
       </c>
       <c r="C381" t="n">
-        <v>90.06999999999999</v>
+        <v>105.44</v>
       </c>
       <c r="D381" t="n">
-        <v>20107</v>
+        <v>23481</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>95.79000000000001</v>
+        <v>135.32</v>
       </c>
       <c r="B382" t="n">
-        <v>36650</v>
+        <v>20605</v>
       </c>
       <c r="C382" t="n">
-        <v>94.33</v>
+        <v>126.3</v>
       </c>
       <c r="D382" t="n">
-        <v>19946</v>
+        <v>27161</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>90.90000000000001</v>
+        <v>135.41</v>
       </c>
       <c r="B383" t="n">
-        <v>24927</v>
+        <v>16871</v>
       </c>
       <c r="C383" t="n">
-        <v>94.33</v>
+        <v>137.14</v>
       </c>
       <c r="D383" t="n">
-        <v>27609</v>
+        <v>13147</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>113.53</v>
+        <v>135.52</v>
       </c>
       <c r="B384" t="n">
-        <v>27438</v>
+        <v>22079</v>
       </c>
       <c r="C384" t="n">
-        <v>116.85</v>
+        <v>132.96</v>
       </c>
       <c r="D384" t="n">
-        <v>27106</v>
+        <v>22268</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>91.36</v>
+        <v>135.66</v>
       </c>
       <c r="B385" t="n">
-        <v>25432</v>
+        <v>17369</v>
       </c>
       <c r="C385" t="n">
-        <v>94.51000000000001</v>
+        <v>120.29</v>
       </c>
       <c r="D385" t="n">
-        <v>29620</v>
+        <v>14307</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>114.6</v>
+        <v>136.49</v>
       </c>
       <c r="B386" t="n">
-        <v>20816</v>
+        <v>16575</v>
       </c>
       <c r="C386" t="n">
-        <v>111.26</v>
+        <v>113.65</v>
       </c>
       <c r="D386" t="n">
-        <v>28695</v>
+        <v>29727</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>92.53</v>
+        <v>136.52</v>
       </c>
       <c r="B387" t="n">
-        <v>26407</v>
+        <v>19752</v>
       </c>
       <c r="C387" t="n">
-        <v>93.83</v>
+        <v>157.78</v>
       </c>
       <c r="D387" t="n">
-        <v>29399</v>
+        <v>11284</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>102.55</v>
+        <v>136.8</v>
       </c>
       <c r="B388" t="n">
-        <v>47014</v>
+        <v>20685</v>
       </c>
       <c r="C388" t="n">
-        <v>99.70999999999999</v>
+        <v>121.91</v>
       </c>
       <c r="D388" t="n">
-        <v>17292</v>
+        <v>10740</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>114.04</v>
+        <v>138.77</v>
       </c>
       <c r="B389" t="n">
-        <v>24290</v>
+        <v>17484</v>
       </c>
       <c r="C389" t="n">
-        <v>113.24</v>
+        <v>142.15</v>
       </c>
       <c r="D389" t="n">
-        <v>24129</v>
+        <v>12248</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>101.15</v>
+        <v>139.13</v>
       </c>
       <c r="B390" t="n">
-        <v>47160</v>
+        <v>19026</v>
       </c>
       <c r="C390" t="n">
-        <v>102.5</v>
+        <v>132.03</v>
       </c>
       <c r="D390" t="n">
-        <v>10913</v>
+        <v>27128</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>96.27</v>
+        <v>139.17</v>
       </c>
       <c r="B391" t="n">
-        <v>39676</v>
+        <v>21115</v>
       </c>
       <c r="C391" t="n">
-        <v>96.64</v>
+        <v>150.54</v>
       </c>
       <c r="D391" t="n">
-        <v>20111</v>
+        <v>26586</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>94.09</v>
+        <v>139.77</v>
       </c>
       <c r="B392" t="n">
-        <v>29117</v>
+        <v>19405</v>
       </c>
       <c r="C392" t="n">
-        <v>94.84999999999999</v>
+        <v>150.86</v>
       </c>
       <c r="D392" t="n">
-        <v>10998</v>
+        <v>15277</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>91.36</v>
+        <v>140.14</v>
       </c>
       <c r="B393" t="n">
-        <v>23792</v>
+        <v>19139</v>
       </c>
       <c r="C393" t="n">
-        <v>90.94</v>
+        <v>133.57</v>
       </c>
       <c r="D393" t="n">
-        <v>17064</v>
+        <v>24318</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>154.99</v>
+        <v>140.26</v>
       </c>
       <c r="B394" t="n">
-        <v>23074</v>
+        <v>20911</v>
       </c>
       <c r="C394" t="n">
-        <v>157.16</v>
+        <v>136</v>
       </c>
       <c r="D394" t="n">
-        <v>29724</v>
+        <v>19948</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>30.45</v>
+        <v>140.71</v>
       </c>
       <c r="B395" t="n">
-        <v>23597</v>
+        <v>18387</v>
       </c>
       <c r="C395" t="n">
-        <v>31.35</v>
+        <v>115.91</v>
       </c>
       <c r="D395" t="n">
-        <v>14619</v>
+        <v>29155</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>101.46</v>
+        <v>140.82</v>
       </c>
       <c r="B396" t="n">
-        <v>46902</v>
+        <v>19925</v>
       </c>
       <c r="C396" t="n">
-        <v>104.45</v>
+        <v>106.34</v>
       </c>
       <c r="D396" t="n">
-        <v>18461</v>
+        <v>26753</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>98.62</v>
+        <v>141.84</v>
       </c>
       <c r="B397" t="n">
-        <v>41221</v>
+        <v>22426</v>
       </c>
       <c r="C397" t="n">
-        <v>99.73999999999999</v>
+        <v>120.68</v>
       </c>
       <c r="D397" t="n">
-        <v>27696</v>
+        <v>25077</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>114.6</v>
+        <v>141.93</v>
       </c>
       <c r="B398" t="n">
-        <v>22024</v>
+        <v>22447</v>
       </c>
       <c r="C398" t="n">
-        <v>111.7</v>
+        <v>126.81</v>
       </c>
       <c r="D398" t="n">
-        <v>11916</v>
+        <v>27738</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>96.20999999999999</v>
+        <v>142.74</v>
       </c>
       <c r="B399" t="n">
-        <v>36825</v>
+        <v>20045</v>
       </c>
       <c r="C399" t="n">
-        <v>98.44</v>
+        <v>160.33</v>
       </c>
       <c r="D399" t="n">
-        <v>17564</v>
+        <v>12963</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>103.6</v>
+        <v>142.76</v>
       </c>
       <c r="B400" t="n">
-        <v>48763</v>
+        <v>20451</v>
       </c>
       <c r="C400" t="n">
-        <v>104.12</v>
+        <v>166.18</v>
       </c>
       <c r="D400" t="n">
-        <v>24857</v>
+        <v>12141</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>100.12</v>
+        <v>142.97</v>
       </c>
       <c r="B401" t="n">
-        <v>44244</v>
+        <v>18965</v>
       </c>
       <c r="C401" t="n">
-        <v>97.19</v>
+        <v>129.13</v>
       </c>
       <c r="D401" t="n">
-        <v>10753</v>
+        <v>12160</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>107.79</v>
+        <v>143.36</v>
       </c>
       <c r="B402" t="n">
-        <v>41501</v>
+        <v>17798</v>
       </c>
       <c r="C402" t="n">
-        <v>106.28</v>
+        <v>164.9</v>
       </c>
       <c r="D402" t="n">
-        <v>11813</v>
+        <v>18284</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>93.26000000000001</v>
+        <v>144.46</v>
       </c>
       <c r="B403" t="n">
-        <v>30244</v>
+        <v>22623</v>
       </c>
       <c r="C403" t="n">
-        <v>90.98</v>
+        <v>136.89</v>
       </c>
       <c r="D403" t="n">
-        <v>15466</v>
+        <v>29124</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>94.18000000000001</v>
+        <v>145.24</v>
       </c>
       <c r="B404" t="n">
-        <v>30721</v>
+        <v>16540</v>
       </c>
       <c r="C404" t="n">
-        <v>96.92</v>
+        <v>117.87</v>
       </c>
       <c r="D404" t="n">
-        <v>25936</v>
+        <v>29280</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>113.46</v>
+        <v>146.17</v>
       </c>
       <c r="B405" t="n">
-        <v>20439</v>
+        <v>22561</v>
       </c>
       <c r="C405" t="n">
-        <v>115.28</v>
+        <v>147.12</v>
       </c>
       <c r="D405" t="n">
-        <v>24355</v>
+        <v>23169</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>113.9</v>
+        <v>146.78</v>
       </c>
       <c r="B406" t="n">
-        <v>24215</v>
+        <v>20505</v>
       </c>
       <c r="C406" t="n">
-        <v>109.29</v>
+        <v>145.53</v>
       </c>
       <c r="D406" t="n">
-        <v>29377</v>
+        <v>23517</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>92.88</v>
+        <v>146.79</v>
       </c>
       <c r="B407" t="n">
-        <v>24915</v>
+        <v>19805</v>
       </c>
       <c r="C407" t="n">
-        <v>90.25</v>
+        <v>150.69</v>
       </c>
       <c r="D407" t="n">
-        <v>21894</v>
+        <v>27234</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>127.36</v>
+        <v>147.5</v>
       </c>
       <c r="B408" t="n">
-        <v>24097</v>
+        <v>19442</v>
       </c>
       <c r="C408" t="n">
-        <v>131.89</v>
+        <v>135.83</v>
       </c>
       <c r="D408" t="n">
-        <v>23467</v>
+        <v>21022</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>102.73</v>
+        <v>147.59</v>
       </c>
       <c r="B409" t="n">
-        <v>47298</v>
+        <v>20978</v>
       </c>
       <c r="C409" t="n">
-        <v>103.71</v>
+        <v>117.99</v>
       </c>
       <c r="D409" t="n">
-        <v>10352</v>
+        <v>24223</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>108.06</v>
+        <v>147.81</v>
       </c>
       <c r="B410" t="n">
-        <v>38501</v>
+        <v>22786</v>
       </c>
       <c r="C410" t="n">
-        <v>110.95</v>
+        <v>159.27</v>
       </c>
       <c r="D410" t="n">
-        <v>20810</v>
+        <v>18325</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>107.78</v>
+        <v>147.94</v>
       </c>
       <c r="B411" t="n">
-        <v>41911</v>
+        <v>20670</v>
       </c>
       <c r="C411" t="n">
-        <v>104.94</v>
+        <v>116.31</v>
       </c>
       <c r="D411" t="n">
-        <v>26172</v>
+        <v>21168</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>28.3</v>
+        <v>148.84</v>
       </c>
       <c r="B412" t="n">
-        <v>23334</v>
+        <v>21136</v>
       </c>
       <c r="C412" t="n">
-        <v>27.17</v>
+        <v>124.22</v>
       </c>
       <c r="D412" t="n">
-        <v>17645</v>
+        <v>11386</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>157.88</v>
+        <v>148.84</v>
       </c>
       <c r="B413" t="n">
-        <v>23438</v>
+        <v>22747</v>
       </c>
       <c r="C413" t="n">
-        <v>160.07</v>
+        <v>177.13</v>
       </c>
       <c r="D413" t="n">
-        <v>18258</v>
+        <v>16946</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>105.48</v>
+        <v>148.87</v>
       </c>
       <c r="B414" t="n">
-        <v>45146</v>
+        <v>21432</v>
       </c>
       <c r="C414" t="n">
-        <v>104.18</v>
+        <v>174.67</v>
       </c>
       <c r="D414" t="n">
-        <v>23475</v>
+        <v>24788</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>129.42</v>
+        <v>149.08</v>
       </c>
       <c r="B415" t="n">
-        <v>23865</v>
+        <v>25624</v>
       </c>
       <c r="C415" t="n">
-        <v>130.66</v>
+        <v>139.65</v>
       </c>
       <c r="D415" t="n">
-        <v>28412</v>
+        <v>20184</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>104.75</v>
+        <v>149.14</v>
       </c>
       <c r="B416" t="n">
-        <v>47167</v>
+        <v>23684</v>
       </c>
       <c r="C416" t="n">
-        <v>107.21</v>
+        <v>132.83</v>
       </c>
       <c r="D416" t="n">
-        <v>29668</v>
+        <v>27100</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>85.81999999999999</v>
+        <v>149.36</v>
       </c>
       <c r="B417" t="n">
-        <v>24142</v>
+        <v>21908</v>
       </c>
       <c r="C417" t="n">
-        <v>87.90000000000001</v>
+        <v>167.17</v>
       </c>
       <c r="D417" t="n">
-        <v>10810</v>
+        <v>19853</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>109.06</v>
+        <v>149.64</v>
       </c>
       <c r="B418" t="n">
-        <v>37671</v>
+        <v>22880</v>
       </c>
       <c r="C418" t="n">
-        <v>111.63</v>
+        <v>171.24</v>
       </c>
       <c r="D418" t="n">
-        <v>17864</v>
+        <v>23639</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>112.32</v>
+        <v>151.62</v>
       </c>
       <c r="B419" t="n">
-        <v>25593</v>
+        <v>26656</v>
       </c>
       <c r="C419" t="n">
-        <v>110.14</v>
+        <v>133.18</v>
       </c>
       <c r="D419" t="n">
-        <v>28263</v>
+        <v>13082</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>104.72</v>
+        <v>151.93</v>
       </c>
       <c r="B420" t="n">
-        <v>45330</v>
+        <v>25073</v>
       </c>
       <c r="C420" t="n">
-        <v>100.67</v>
+        <v>179.41</v>
       </c>
       <c r="D420" t="n">
-        <v>23626</v>
+        <v>16291</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>113.73</v>
+        <v>152.44</v>
       </c>
       <c r="B421" t="n">
-        <v>23871</v>
+        <v>25799</v>
       </c>
       <c r="C421" t="n">
-        <v>112.84</v>
+        <v>171.47</v>
       </c>
       <c r="D421" t="n">
-        <v>17535</v>
+        <v>18637</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>95.66</v>
+        <v>153.05</v>
       </c>
       <c r="B422" t="n">
-        <v>35007</v>
+        <v>27680</v>
       </c>
       <c r="C422" t="n">
-        <v>92.86</v>
+        <v>136.05</v>
       </c>
       <c r="D422" t="n">
-        <v>20218</v>
+        <v>25976</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>5.74</v>
+        <v>153.15</v>
       </c>
       <c r="B423" t="n">
-        <v>24072</v>
+        <v>27857</v>
       </c>
       <c r="C423" t="n">
-        <v>6.01</v>
+        <v>173.85</v>
       </c>
       <c r="D423" t="n">
-        <v>15604</v>
+        <v>27933</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>112.29</v>
+        <v>154.3</v>
       </c>
       <c r="B424" t="n">
-        <v>28176</v>
+        <v>24086</v>
       </c>
       <c r="C424" t="n">
-        <v>109.05</v>
+        <v>155.87</v>
       </c>
       <c r="D424" t="n">
-        <v>26049</v>
+        <v>20163</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>103.8</v>
+        <v>154.36</v>
       </c>
       <c r="B425" t="n">
-        <v>46293</v>
+        <v>29005</v>
       </c>
       <c r="C425" t="n">
-        <v>106.99</v>
+        <v>126.72</v>
       </c>
       <c r="D425" t="n">
-        <v>19560</v>
+        <v>22139</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>90.42</v>
+        <v>154.38</v>
       </c>
       <c r="B426" t="n">
-        <v>24194</v>
+        <v>24458</v>
       </c>
       <c r="C426" t="n">
-        <v>89.7</v>
+        <v>171.88</v>
       </c>
       <c r="D426" t="n">
-        <v>22429</v>
+        <v>29225</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>100.87</v>
+        <v>154.66</v>
       </c>
       <c r="B427" t="n">
-        <v>44618</v>
+        <v>26254</v>
       </c>
       <c r="C427" t="n">
-        <v>101.97</v>
+        <v>169.82</v>
       </c>
       <c r="D427" t="n">
-        <v>16578</v>
+        <v>10854</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>97.95</v>
+        <v>154.72</v>
       </c>
       <c r="B428" t="n">
-        <v>39842</v>
+        <v>26646</v>
       </c>
       <c r="C428" t="n">
-        <v>100.08</v>
+        <v>130.83</v>
       </c>
       <c r="D428" t="n">
-        <v>23937</v>
+        <v>17405</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>127.78</v>
+        <v>154.93</v>
       </c>
       <c r="B429" t="n">
-        <v>21647</v>
+        <v>25998</v>
       </c>
       <c r="C429" t="n">
-        <v>123.86</v>
+        <v>138.91</v>
       </c>
       <c r="D429" t="n">
-        <v>10869</v>
+        <v>21716</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>93.17</v>
+        <v>155.83</v>
       </c>
       <c r="B430" t="n">
-        <v>29432</v>
+        <v>32419</v>
       </c>
       <c r="C430" t="n">
-        <v>93.38</v>
+        <v>133.48</v>
       </c>
       <c r="D430" t="n">
-        <v>20467</v>
+        <v>23028</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>98.7</v>
+        <v>156.06</v>
       </c>
       <c r="B431" t="n">
-        <v>43462</v>
+        <v>26827</v>
       </c>
       <c r="C431" t="n">
-        <v>94.89</v>
+        <v>161.29</v>
       </c>
       <c r="D431" t="n">
-        <v>25941</v>
+        <v>17259</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>95.58</v>
+        <v>156.64</v>
       </c>
       <c r="B432" t="n">
-        <v>35679</v>
+        <v>28194</v>
       </c>
       <c r="C432" t="n">
-        <v>93.31</v>
+        <v>152.38</v>
       </c>
       <c r="D432" t="n">
-        <v>11374</v>
+        <v>27734</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>101.2</v>
+        <v>157.13</v>
       </c>
       <c r="B433" t="n">
-        <v>47192</v>
+        <v>30860</v>
       </c>
       <c r="C433" t="n">
-        <v>100.16</v>
+        <v>147.83</v>
       </c>
       <c r="D433" t="n">
-        <v>19423</v>
+        <v>24175</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>105.93</v>
+        <v>157.56</v>
       </c>
       <c r="B434" t="n">
-        <v>43640</v>
+        <v>30881</v>
       </c>
       <c r="C434" t="n">
-        <v>108.8</v>
+        <v>137.01</v>
       </c>
       <c r="D434" t="n">
-        <v>14106</v>
+        <v>12959</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>99.5</v>
+        <v>157.65</v>
       </c>
       <c r="B435" t="n">
-        <v>42783</v>
+        <v>30653</v>
       </c>
       <c r="C435" t="n">
-        <v>97.65000000000001</v>
+        <v>127.01</v>
       </c>
       <c r="D435" t="n">
-        <v>19577</v>
+        <v>16780</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>108.56</v>
+        <v>158.2</v>
       </c>
       <c r="B436" t="n">
-        <v>36373</v>
+        <v>29792</v>
       </c>
       <c r="C436" t="n">
-        <v>110.63</v>
+        <v>180</v>
       </c>
       <c r="D436" t="n">
-        <v>25325</v>
+        <v>18199</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>66.72</v>
+        <v>158.42</v>
       </c>
       <c r="B437" t="n">
-        <v>23044</v>
+        <v>29820</v>
       </c>
       <c r="C437" t="n">
-        <v>68.34999999999999</v>
+        <v>130.03</v>
       </c>
       <c r="D437" t="n">
-        <v>24702</v>
+        <v>14831</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>175.68</v>
+        <v>158.84</v>
       </c>
       <c r="B438" t="n">
-        <v>24305</v>
+        <v>30516</v>
       </c>
       <c r="C438" t="n">
-        <v>176.15</v>
+        <v>168.57</v>
       </c>
       <c r="D438" t="n">
-        <v>24209</v>
+        <v>22881</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>98.01000000000001</v>
+        <v>159.37</v>
       </c>
       <c r="B439" t="n">
-        <v>39896</v>
+        <v>28167</v>
       </c>
       <c r="C439" t="n">
-        <v>99.81</v>
+        <v>139.53</v>
       </c>
       <c r="D439" t="n">
-        <v>27663</v>
+        <v>20659</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>163.07</v>
+        <v>159.83</v>
       </c>
       <c r="B440" t="n">
-        <v>26267</v>
+        <v>33652</v>
       </c>
       <c r="C440" t="n">
-        <v>163.63</v>
+        <v>170.62</v>
       </c>
       <c r="D440" t="n">
-        <v>19467</v>
+        <v>10116</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>113.42</v>
+        <v>159.96</v>
       </c>
       <c r="B441" t="n">
-        <v>22655</v>
+        <v>30756</v>
       </c>
       <c r="C441" t="n">
-        <v>116.54</v>
+        <v>180</v>
       </c>
       <c r="D441" t="n">
-        <v>27193</v>
+        <v>24701</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>96.75</v>
+        <v>160.04</v>
       </c>
       <c r="B442" t="n">
-        <v>39726</v>
+        <v>29642</v>
       </c>
       <c r="C442" t="n">
-        <v>96.03</v>
+        <v>148.7</v>
       </c>
       <c r="D442" t="n">
-        <v>21776</v>
+        <v>21168</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>107.93</v>
+        <v>160.99</v>
       </c>
       <c r="B443" t="n">
-        <v>39031</v>
+        <v>30848</v>
       </c>
       <c r="C443" t="n">
-        <v>106.54</v>
+        <v>180</v>
       </c>
       <c r="D443" t="n">
-        <v>19246</v>
+        <v>20979</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>109.71</v>
+        <v>161.07</v>
       </c>
       <c r="B444" t="n">
-        <v>31708</v>
+        <v>29524</v>
       </c>
       <c r="C444" t="n">
-        <v>113.21</v>
+        <v>170.65</v>
       </c>
       <c r="D444" t="n">
-        <v>26125</v>
+        <v>18324</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>100.25</v>
+        <v>161.47</v>
       </c>
       <c r="B445" t="n">
-        <v>43627</v>
+        <v>30701</v>
       </c>
       <c r="C445" t="n">
-        <v>101.98</v>
+        <v>147.31</v>
       </c>
       <c r="D445" t="n">
-        <v>22265</v>
+        <v>25706</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>123.38</v>
+        <v>161.51</v>
       </c>
       <c r="B446" t="n">
-        <v>23802</v>
+        <v>29246</v>
       </c>
       <c r="C446" t="n">
-        <v>123.99</v>
+        <v>140.96</v>
       </c>
       <c r="D446" t="n">
-        <v>24928</v>
+        <v>20654</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>97.08</v>
+        <v>162.03</v>
       </c>
       <c r="B447" t="n">
-        <v>39372</v>
+        <v>29205</v>
       </c>
       <c r="C447" t="n">
-        <v>94.23999999999999</v>
+        <v>150.76</v>
       </c>
       <c r="D447" t="n">
-        <v>23894</v>
+        <v>15864</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>67.20999999999999</v>
+        <v>162.29</v>
       </c>
       <c r="B448" t="n">
-        <v>23047</v>
+        <v>30275</v>
       </c>
       <c r="C448" t="n">
-        <v>64.56999999999999</v>
+        <v>180</v>
       </c>
       <c r="D448" t="n">
-        <v>18338</v>
+        <v>20296</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>110.35</v>
+        <v>163.15</v>
       </c>
       <c r="B449" t="n">
-        <v>34972</v>
+        <v>28262</v>
       </c>
       <c r="C449" t="n">
-        <v>109.79</v>
+        <v>133.98</v>
       </c>
       <c r="D449" t="n">
-        <v>17840</v>
+        <v>25185</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>112.02</v>
+        <v>163.15</v>
       </c>
       <c r="B450" t="n">
-        <v>28029</v>
+        <v>30181</v>
       </c>
       <c r="C450" t="n">
-        <v>111.65</v>
+        <v>150.54</v>
       </c>
       <c r="D450" t="n">
-        <v>19751</v>
+        <v>10840</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>102.57</v>
+        <v>163.18</v>
       </c>
       <c r="B451" t="n">
-        <v>48962</v>
+        <v>28176</v>
       </c>
       <c r="C451" t="n">
-        <v>105.7</v>
+        <v>138.94</v>
       </c>
       <c r="D451" t="n">
-        <v>18988</v>
+        <v>29411</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>109.17</v>
+        <v>163.39</v>
       </c>
       <c r="B452" t="n">
-        <v>33954</v>
+        <v>30427</v>
       </c>
       <c r="C452" t="n">
-        <v>106.11</v>
+        <v>170.97</v>
       </c>
       <c r="D452" t="n">
-        <v>18898</v>
+        <v>17182</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>143.08</v>
+        <v>163.53</v>
       </c>
       <c r="B453" t="n">
-        <v>24349</v>
+        <v>29612</v>
       </c>
       <c r="C453" t="n">
-        <v>138.89</v>
+        <v>157.66</v>
       </c>
       <c r="D453" t="n">
-        <v>25720</v>
+        <v>10081</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>94.81999999999999</v>
+        <v>163.64</v>
       </c>
       <c r="B454" t="n">
-        <v>30957</v>
+        <v>26574</v>
       </c>
       <c r="C454" t="n">
-        <v>98.88</v>
+        <v>180</v>
       </c>
       <c r="D454" t="n">
-        <v>25160</v>
+        <v>27085</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>90.06999999999999</v>
+        <v>163.77</v>
       </c>
       <c r="B455" t="n">
-        <v>24003</v>
+        <v>28468</v>
       </c>
       <c r="C455" t="n">
-        <v>87.66</v>
+        <v>128.03</v>
       </c>
       <c r="D455" t="n">
-        <v>18355</v>
+        <v>15607</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>113.72</v>
+        <v>163.88</v>
       </c>
       <c r="B456" t="n">
-        <v>24150</v>
+        <v>31682</v>
       </c>
       <c r="C456" t="n">
-        <v>117.45</v>
+        <v>180</v>
       </c>
       <c r="D456" t="n">
-        <v>21104</v>
+        <v>16376</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>103.19</v>
+        <v>165.41</v>
       </c>
       <c r="B457" t="n">
-        <v>48537</v>
+        <v>27020</v>
       </c>
       <c r="C457" t="n">
-        <v>101.06</v>
+        <v>163.43</v>
       </c>
       <c r="D457" t="n">
-        <v>26262</v>
+        <v>20036</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>94.19</v>
+        <v>166.09</v>
       </c>
       <c r="B458" t="n">
-        <v>29276</v>
+        <v>27735</v>
       </c>
       <c r="C458" t="n">
-        <v>95.48</v>
+        <v>180</v>
       </c>
       <c r="D458" t="n">
-        <v>27784</v>
+        <v>23686</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>101.92</v>
+        <v>166.26</v>
       </c>
       <c r="B459" t="n">
-        <v>47184</v>
+        <v>26673</v>
       </c>
       <c r="C459" t="n">
-        <v>100.69</v>
+        <v>169.46</v>
       </c>
       <c r="D459" t="n">
-        <v>22996</v>
+        <v>13507</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>96.39</v>
+        <v>166.43</v>
       </c>
       <c r="B460" t="n">
-        <v>38731</v>
+        <v>24195</v>
       </c>
       <c r="C460" t="n">
-        <v>93.15000000000001</v>
+        <v>180</v>
       </c>
       <c r="D460" t="n">
-        <v>27558</v>
+        <v>18126</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>97.95</v>
+        <v>166.51</v>
       </c>
       <c r="B461" t="n">
-        <v>39930</v>
+        <v>26724</v>
       </c>
       <c r="C461" t="n">
-        <v>97.39</v>
+        <v>161.22</v>
       </c>
       <c r="D461" t="n">
-        <v>23225</v>
+        <v>15049</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>41.87</v>
+        <v>166.73</v>
       </c>
       <c r="B462" t="n">
-        <v>21943</v>
+        <v>27575</v>
       </c>
       <c r="C462" t="n">
-        <v>43.08</v>
+        <v>156.37</v>
       </c>
       <c r="D462" t="n">
-        <v>18710</v>
+        <v>26882</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>130.83</v>
+        <v>167.6</v>
       </c>
       <c r="B463" t="n">
-        <v>22120</v>
+        <v>25092</v>
       </c>
       <c r="C463" t="n">
-        <v>134.52</v>
+        <v>180</v>
       </c>
       <c r="D463" t="n">
-        <v>18576</v>
+        <v>27279</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>109.69</v>
+        <v>169.7</v>
       </c>
       <c r="B464" t="n">
-        <v>34440</v>
+        <v>23193</v>
       </c>
       <c r="C464" t="n">
-        <v>106.39</v>
+        <v>144.12</v>
       </c>
       <c r="D464" t="n">
-        <v>27029</v>
+        <v>28258</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>101.87</v>
+        <v>170.6</v>
       </c>
       <c r="B465" t="n">
-        <v>49253</v>
+        <v>23597</v>
       </c>
       <c r="C465" t="n">
-        <v>97.61</v>
+        <v>153.6</v>
       </c>
       <c r="D465" t="n">
-        <v>22486</v>
+        <v>18096</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>103.78</v>
+        <v>170.7</v>
       </c>
       <c r="B466" t="n">
-        <v>46712</v>
+        <v>23252</v>
       </c>
       <c r="C466" t="n">
-        <v>106.31</v>
+        <v>180</v>
       </c>
       <c r="D466" t="n">
-        <v>19063</v>
+        <v>27059</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>95.97</v>
+        <v>170.94</v>
       </c>
       <c r="B467" t="n">
-        <v>36123</v>
+        <v>20538</v>
       </c>
       <c r="C467" t="n">
-        <v>97.8</v>
+        <v>180</v>
       </c>
       <c r="D467" t="n">
-        <v>22608</v>
+        <v>23393</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>67.62</v>
+        <v>172.11</v>
       </c>
       <c r="B468" t="n">
-        <v>23026</v>
+        <v>21931</v>
       </c>
       <c r="C468" t="n">
-        <v>67.31999999999999</v>
+        <v>180</v>
       </c>
       <c r="D468" t="n">
-        <v>13038</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>91.29000000000001</v>
+        <v>172.25</v>
       </c>
       <c r="B469" t="n">
-        <v>23547</v>
+        <v>22416</v>
       </c>
       <c r="C469" t="n">
-        <v>88.94</v>
+        <v>180</v>
       </c>
       <c r="D469" t="n">
-        <v>24361</v>
+        <v>13694</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>167.05</v>
+        <v>172.29</v>
       </c>
       <c r="B470" t="n">
-        <v>23928</v>
+        <v>22562</v>
       </c>
       <c r="C470" t="n">
-        <v>170.56</v>
+        <v>180</v>
       </c>
       <c r="D470" t="n">
-        <v>23284</v>
+        <v>20143</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>112.93</v>
+        <v>172.63</v>
       </c>
       <c r="B471" t="n">
-        <v>26177</v>
+        <v>20785</v>
       </c>
       <c r="C471" t="n">
-        <v>109</v>
+        <v>163.92</v>
       </c>
       <c r="D471" t="n">
-        <v>12734</v>
+        <v>29171</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>14.05</v>
+        <v>173.04</v>
       </c>
       <c r="B472" t="n">
-        <v>23846</v>
+        <v>21134</v>
       </c>
       <c r="C472" t="n">
-        <v>15.14</v>
+        <v>143.08</v>
       </c>
       <c r="D472" t="n">
-        <v>23642</v>
+        <v>23758</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>114.64</v>
+        <v>173.22</v>
       </c>
       <c r="B473" t="n">
-        <v>22190</v>
+        <v>20830</v>
       </c>
       <c r="C473" t="n">
-        <v>117</v>
+        <v>152.16</v>
       </c>
       <c r="D473" t="n">
-        <v>19339</v>
+        <v>26794</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>102.4</v>
+        <v>173.39</v>
       </c>
       <c r="B474" t="n">
-        <v>43632</v>
+        <v>19885</v>
       </c>
       <c r="C474" t="n">
-        <v>104.59</v>
+        <v>144.31</v>
       </c>
       <c r="D474" t="n">
-        <v>23666</v>
+        <v>16807</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>108.8</v>
+        <v>173.53</v>
       </c>
       <c r="B475" t="n">
-        <v>34410</v>
+        <v>20487</v>
       </c>
       <c r="C475" t="n">
-        <v>109.08</v>
+        <v>139.99</v>
       </c>
       <c r="D475" t="n">
-        <v>11369</v>
+        <v>19842</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>142.04</v>
+        <v>174.06</v>
       </c>
       <c r="B476" t="n">
-        <v>23342</v>
+        <v>20985</v>
       </c>
       <c r="C476" t="n">
-        <v>145.05</v>
+        <v>180</v>
       </c>
       <c r="D476" t="n">
-        <v>17860</v>
+        <v>15229</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>98.28</v>
+        <v>174.15</v>
       </c>
       <c r="B477" t="n">
-        <v>39685</v>
+        <v>21593</v>
       </c>
       <c r="C477" t="n">
-        <v>97.70999999999999</v>
+        <v>170.61</v>
       </c>
       <c r="D477" t="n">
-        <v>24215</v>
+        <v>29736</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>86.95999999999999</v>
+        <v>174.4</v>
       </c>
       <c r="B478" t="n">
-        <v>23970</v>
+        <v>18738</v>
       </c>
       <c r="C478" t="n">
-        <v>86.19</v>
+        <v>180</v>
       </c>
       <c r="D478" t="n">
-        <v>17180</v>
+        <v>21464</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>111.38</v>
+        <v>174.53</v>
       </c>
       <c r="B479" t="n">
-        <v>30263</v>
+        <v>19018</v>
       </c>
       <c r="C479" t="n">
-        <v>115.74</v>
+        <v>168.2</v>
       </c>
       <c r="D479" t="n">
-        <v>18390</v>
+        <v>24140</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>90.73999999999999</v>
+        <v>175.08</v>
       </c>
       <c r="B480" t="n">
-        <v>22068</v>
+        <v>19784</v>
       </c>
       <c r="C480" t="n">
-        <v>92.56999999999999</v>
+        <v>163.67</v>
       </c>
       <c r="D480" t="n">
-        <v>16679</v>
+        <v>21528</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>95.12</v>
+        <v>175.44</v>
       </c>
       <c r="B481" t="n">
-        <v>35510</v>
+        <v>19091</v>
       </c>
       <c r="C481" t="n">
-        <v>98.95999999999999</v>
+        <v>180</v>
       </c>
       <c r="D481" t="n">
-        <v>20649</v>
+        <v>16853</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>98.31</v>
+        <v>175.62</v>
       </c>
       <c r="B482" t="n">
-        <v>42350</v>
+        <v>18005</v>
       </c>
       <c r="C482" t="n">
-        <v>99.93000000000001</v>
+        <v>180</v>
       </c>
       <c r="D482" t="n">
-        <v>11145</v>
+        <v>21123</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>105.9</v>
+        <v>175.63</v>
       </c>
       <c r="B483" t="n">
-        <v>45313</v>
+        <v>18592</v>
       </c>
       <c r="C483" t="n">
-        <v>109.46</v>
+        <v>169.98</v>
       </c>
       <c r="D483" t="n">
-        <v>29193</v>
+        <v>12298</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>106.83</v>
+        <v>175.81</v>
       </c>
       <c r="B484" t="n">
-        <v>40444</v>
+        <v>18500</v>
       </c>
       <c r="C484" t="n">
-        <v>109.85</v>
+        <v>178.81</v>
       </c>
       <c r="D484" t="n">
-        <v>12820</v>
+        <v>26253</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>102.76</v>
+        <v>176.37</v>
       </c>
       <c r="B485" t="n">
-        <v>46899</v>
+        <v>17359</v>
       </c>
       <c r="C485" t="n">
-        <v>102.53</v>
+        <v>144.37</v>
       </c>
       <c r="D485" t="n">
-        <v>13861</v>
+        <v>28059</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>94.31999999999999</v>
+        <v>176.51</v>
       </c>
       <c r="B486" t="n">
-        <v>30570</v>
+        <v>20027</v>
       </c>
       <c r="C486" t="n">
-        <v>98.51000000000001</v>
+        <v>180</v>
       </c>
       <c r="D486" t="n">
-        <v>17185</v>
+        <v>21414</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>38.01</v>
+        <v>177</v>
       </c>
       <c r="B487" t="n">
-        <v>23172</v>
+        <v>19489</v>
       </c>
       <c r="C487" t="n">
-        <v>37.84</v>
+        <v>168.81</v>
       </c>
       <c r="D487" t="n">
-        <v>25366</v>
+        <v>15996</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>114.09</v>
+        <v>177.49</v>
       </c>
       <c r="B488" t="n">
-        <v>24469</v>
+        <v>18279</v>
       </c>
       <c r="C488" t="n">
-        <v>116.75</v>
+        <v>169.78</v>
       </c>
       <c r="D488" t="n">
-        <v>23326</v>
+        <v>24479</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>109.67</v>
+        <v>177.51</v>
       </c>
       <c r="B489" t="n">
-        <v>31988</v>
+        <v>17787</v>
       </c>
       <c r="C489" t="n">
-        <v>109.25</v>
+        <v>149.52</v>
       </c>
       <c r="D489" t="n">
-        <v>17852</v>
+        <v>13088</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>112.16</v>
+        <v>177.68</v>
       </c>
       <c r="B490" t="n">
-        <v>28996</v>
+        <v>19687</v>
       </c>
       <c r="C490" t="n">
-        <v>108.29</v>
+        <v>149.3</v>
       </c>
       <c r="D490" t="n">
-        <v>14593</v>
+        <v>12610</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>97.25</v>
+        <v>177.69</v>
       </c>
       <c r="B491" t="n">
-        <v>38358</v>
+        <v>19600</v>
       </c>
       <c r="C491" t="n">
-        <v>93.67</v>
+        <v>148.03</v>
       </c>
       <c r="D491" t="n">
-        <v>21175</v>
+        <v>24637</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>133.6</v>
+        <v>177.76</v>
       </c>
       <c r="B492" t="n">
-        <v>23563</v>
+        <v>19977</v>
       </c>
       <c r="C492" t="n">
-        <v>134.25</v>
+        <v>180</v>
       </c>
       <c r="D492" t="n">
-        <v>18317</v>
+        <v>21634</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>105.7</v>
+        <v>177.81</v>
       </c>
       <c r="B493" t="n">
-        <v>45213</v>
+        <v>18123</v>
       </c>
       <c r="C493" t="n">
-        <v>106.48</v>
+        <v>171.28</v>
       </c>
       <c r="D493" t="n">
-        <v>28567</v>
+        <v>21082</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>125.86</v>
+        <v>177.85</v>
       </c>
       <c r="B494" t="n">
-        <v>21001</v>
+        <v>18103</v>
       </c>
       <c r="C494" t="n">
-        <v>127.03</v>
+        <v>180</v>
       </c>
       <c r="D494" t="n">
-        <v>27962</v>
+        <v>23459</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>105.71</v>
+        <v>177.88</v>
       </c>
       <c r="B495" t="n">
-        <v>43635</v>
+        <v>17491</v>
       </c>
       <c r="C495" t="n">
-        <v>107.86</v>
+        <v>180</v>
       </c>
       <c r="D495" t="n">
-        <v>20019</v>
+        <v>24267</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>92.89</v>
+        <v>178.46</v>
       </c>
       <c r="B496" t="n">
-        <v>28285</v>
+        <v>18012</v>
       </c>
       <c r="C496" t="n">
-        <v>95.88</v>
+        <v>180</v>
       </c>
       <c r="D496" t="n">
-        <v>10616</v>
+        <v>26523</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>94.63</v>
+        <v>178.49</v>
       </c>
       <c r="B497" t="n">
-        <v>33521</v>
+        <v>20898</v>
       </c>
       <c r="C497" t="n">
-        <v>97.53</v>
+        <v>174.22</v>
       </c>
       <c r="D497" t="n">
-        <v>20849</v>
+        <v>21515</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>105.66</v>
+        <v>178.64</v>
       </c>
       <c r="B498" t="n">
-        <v>44224</v>
+        <v>19929</v>
       </c>
       <c r="C498" t="n">
-        <v>104.28</v>
+        <v>180</v>
       </c>
       <c r="D498" t="n">
-        <v>29134</v>
+        <v>10084</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>99.25</v>
+        <v>178.9</v>
       </c>
       <c r="B499" t="n">
-        <v>41924</v>
+        <v>18797</v>
       </c>
       <c r="C499" t="n">
-        <v>98.03</v>
+        <v>168.61</v>
       </c>
       <c r="D499" t="n">
-        <v>10219</v>
+        <v>24193</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>114.68</v>
+        <v>179.71</v>
       </c>
       <c r="B500" t="n">
-        <v>24037</v>
+        <v>16819</v>
       </c>
       <c r="C500" t="n">
-        <v>112.84</v>
+        <v>180</v>
       </c>
       <c r="D500" t="n">
-        <v>15361</v>
+        <v>22623</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>113.01</v>
+        <v>179.88</v>
       </c>
       <c r="B501" t="n">
-        <v>24796</v>
+        <v>19220</v>
       </c>
       <c r="C501" t="n">
-        <v>108.27</v>
+        <v>157.16</v>
       </c>
       <c r="D501" t="n">
-        <v>23549</v>
+        <v>10677</v>
       </c>
     </row>
   </sheetData>
